--- a/assets/templates/fp.xlsx
+++ b/assets/templates/fp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\jev-jaro\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DF5738-3786-458E-84AF-667929FBDBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B98AFB8-CCB8-4DDE-84F4-57FD56CAACFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3D37FFD8-D4A5-48D1-ADF7-7A80C174BD04}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Financial Position" sheetId="6" r:id="rId4"/>
     <sheet name="Cash Flows" sheetId="7" r:id="rId5"/>
     <sheet name="Changes in Assets" sheetId="8" r:id="rId6"/>
+    <sheet name="TB" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash Flows'!$A$1:$O$67</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="952">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -2540,6 +2541,369 @@
   </si>
   <si>
     <t>Total recognized revenue and expenses for the period</t>
+  </si>
+  <si>
+    <t>PROVINCE OF LEYTE</t>
+  </si>
+  <si>
+    <t>TRIAL BALANCE</t>
+  </si>
+  <si>
+    <t>ACCOUNT NAME</t>
+  </si>
+  <si>
+    <t>ACCOUNT CODE</t>
+  </si>
+  <si>
+    <t>DEBIT</t>
+  </si>
+  <si>
+    <t>CREDIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petty Cash </t>
+  </si>
+  <si>
+    <t>Cash in Bank-Local Currency, Savings Account</t>
+  </si>
+  <si>
+    <t>Due from GOCCs</t>
+  </si>
+  <si>
+    <t>Due from LGUs</t>
+  </si>
+  <si>
+    <t>Advances for Officers &amp; Employees</t>
+  </si>
+  <si>
+    <t>Receivables- Disallowances/Charges</t>
+  </si>
+  <si>
+    <t>Property &amp; Equipment for Distribution</t>
+  </si>
+  <si>
+    <t>Drugs &amp; Medicines Inventory</t>
+  </si>
+  <si>
+    <t>Medical, Dental &amp; Laboratory Supplies Inventory</t>
+  </si>
+  <si>
+    <t>Agricultural &amp; Marine Supplies Inventory</t>
+  </si>
+  <si>
+    <t>Other Supplies &amp; Materials Inventory</t>
+  </si>
+  <si>
+    <t>Construction in Progress-Investment Property, Buildings</t>
+  </si>
+  <si>
+    <t>Land Improvements, Aquaculture Structures</t>
+  </si>
+  <si>
+    <t>Flood Control Sysems</t>
+  </si>
+  <si>
+    <t>Water Supply System</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Power Supply Systems</t>
+  </si>
+  <si>
+    <t>School Buildings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markets </t>
+  </si>
+  <si>
+    <t>Slaughterhouse</t>
+  </si>
+  <si>
+    <t>Other Structure</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Machinery</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Office Equipment</t>
+  </si>
+  <si>
+    <t>Information &amp; Communication Technology Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Information &amp; Communication Technology Equipment</t>
+  </si>
+  <si>
+    <t>Agricultural &amp; Forestry Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Agricultural &amp; Forestry Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Communication Equipment</t>
+  </si>
+  <si>
+    <t>Construction &amp; Heavy Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Construction &amp; Heavy Equipment</t>
+  </si>
+  <si>
+    <t>Disaster Response &amp; Rescue Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation-Disaster Response &amp; Rescue Equipment</t>
+  </si>
+  <si>
+    <t>Military, Police &amp; Security Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation-Military, Police &amp; Security Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Medical Equipment</t>
+  </si>
+  <si>
+    <t>Technical &amp; Scientific Equipment</t>
+  </si>
+  <si>
+    <t>Other Machinery &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Other Machinery &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Motor Vehicles</t>
+  </si>
+  <si>
+    <t>Furniture &amp; Fixtures</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Furniture &amp; Fixtures</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>Construction in Progress- Land Improvements</t>
+  </si>
+  <si>
+    <t>Construction in Progress- Infrastructure Assets</t>
+  </si>
+  <si>
+    <t>Construction in Progress-Buildings &amp; Other Structures</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Books</t>
+  </si>
+  <si>
+    <t>Other Property, Plant &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation- Other Property, Plant &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Due to Officers &amp; Employees</t>
+  </si>
+  <si>
+    <t>Loans Payable-Domestic</t>
+  </si>
+  <si>
+    <t>Due to PAG-IBIG</t>
+  </si>
+  <si>
+    <t>Due to PHILHEALTH</t>
+  </si>
+  <si>
+    <t>Guaranty/Security Deposits Payable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deferred Real Property Tax </t>
+  </si>
+  <si>
+    <t>Prior Period Adjustment</t>
+  </si>
+  <si>
+    <t>Community Tax</t>
+  </si>
+  <si>
+    <t>Real Property Tax-Basic</t>
+  </si>
+  <si>
+    <t>Business Tax</t>
+  </si>
+  <si>
+    <t>Tax on Sand, Gravel &amp; Other Quarry Products</t>
+  </si>
+  <si>
+    <t>Tax on Delivery Trucks &amp; Vans</t>
+  </si>
+  <si>
+    <t>Amusement Tax</t>
+  </si>
+  <si>
+    <t>Franchise Tax</t>
+  </si>
+  <si>
+    <t>Tax Revenue- Fines &amp; Penalties- Property Taxes</t>
+  </si>
+  <si>
+    <t>Registration Plates, Tags &amp; Stickers Fees</t>
+  </si>
+  <si>
+    <t>Clearance &amp; Certification Fees</t>
+  </si>
+  <si>
+    <t>Fees for Sealing &amp; Licensing of Weights &amp; Measures</t>
+  </si>
+  <si>
+    <t>Fines &amp; Penalties- Service Income</t>
+  </si>
+  <si>
+    <t>Rent Income</t>
+  </si>
+  <si>
+    <t>Receipt from Slaughterhouse Operation</t>
+  </si>
+  <si>
+    <t>Fines &amp; Penalties- Business Income</t>
+  </si>
+  <si>
+    <t>Subsidy from National Government Agencies (NGAs)</t>
+  </si>
+  <si>
+    <t>Transfer from Gen. Fund as Project Equity Share</t>
+  </si>
+  <si>
+    <t>Grants &amp; Donations in Cash</t>
+  </si>
+  <si>
+    <t>Grants &amp; Donations in Kind</t>
+  </si>
+  <si>
+    <t>Salaries &amp; Wages- Regular</t>
+  </si>
+  <si>
+    <t>Salaries &amp; Wages-Casual/Contractual</t>
+  </si>
+  <si>
+    <t>Personnel Economic Relief Allowance (PERA)</t>
+  </si>
+  <si>
+    <t>Laundry Allowance</t>
+  </si>
+  <si>
+    <t>Overtime &amp; Night Pay</t>
+  </si>
+  <si>
+    <t>Year-End Bonus</t>
+  </si>
+  <si>
+    <t>Other Bonuses &amp; Allowances</t>
+  </si>
+  <si>
+    <t>Retirement &amp; Life Insurance Premiums</t>
+  </si>
+  <si>
+    <t>PAG-IBIG Contributions</t>
+  </si>
+  <si>
+    <t>PHILHEALTH Contributions</t>
+  </si>
+  <si>
+    <t>Traveling Expenses- Local</t>
+  </si>
+  <si>
+    <t>Office Supplies Expenses</t>
+  </si>
+  <si>
+    <t>Non - Accountable Forms Expenses</t>
+  </si>
+  <si>
+    <t>Drugs &amp; Medicines Expenses</t>
+  </si>
+  <si>
+    <t>Medical, Dental &amp; Laboratory Supplies Expenses</t>
+  </si>
+  <si>
+    <t>Fuel, Oil &amp; Lubricants Expenses</t>
+  </si>
+  <si>
+    <t>Agricultural &amp; Marine Supplies Expenses</t>
+  </si>
+  <si>
+    <t>Other Supplies &amp; Materials  Expenses</t>
+  </si>
+  <si>
+    <t>Postage and Courier Services</t>
+  </si>
+  <si>
+    <t>Award/Rewards Expenses</t>
+  </si>
+  <si>
+    <t>Research, Exploration &amp; Development Expenses</t>
+  </si>
+  <si>
+    <t>Extraordinary &amp; Miscellaneous Expenses</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Land Improvements</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Infrastructures &amp; Assets</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Buildings &amp; Other Structures</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Machinery &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Transportation Equipment</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Furniture and Fixtures</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance - Other PPE</t>
+  </si>
+  <si>
+    <t>Subsidy to LGUs</t>
+  </si>
+  <si>
+    <t>Subsidy to Other Funds</t>
+  </si>
+  <si>
+    <t>Transfer of Project Equity Share</t>
+  </si>
+  <si>
+    <t>Taxes, Duties &amp; Licenses</t>
+  </si>
+  <si>
+    <t>Fidelity Bond Premiums</t>
+  </si>
+  <si>
+    <t>Printing &amp; Publication Expenses</t>
+  </si>
+  <si>
+    <t>Membership Dues &amp; Contributions to Organizations</t>
+  </si>
+  <si>
+    <t>Other Maintenance &amp; Operating Expenses</t>
+  </si>
+  <si>
+    <t>Other Financial Charges</t>
+  </si>
+  <si>
+    <t>Depreciation - Machinery &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Depreciation -  Furniture, Fixtures &amp; Books</t>
+  </si>
+  <si>
+    <t>Depreciation - Other Property, Plant &amp; Equipment</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -2550,7 +2914,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="56" x14ac:knownFonts="1">
+  <fonts count="63" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2934,8 +3298,48 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2972,8 +3376,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -3370,6 +3780,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3378,7 +3840,7 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3774,6 +4236,78 @@
     <xf numFmtId="4" fontId="55" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="4" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="60" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="56" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3789,11 +4323,11 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3801,8 +4335,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3810,29 +4344,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3852,53 +4368,41 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3924,16 +4428,46 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3953,6 +4487,33 @@
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4585,6 +5146,95 @@
         <a:xfrm>
           <a:off x="1209674" y="9655"/>
           <a:ext cx="940985" cy="886393"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1857375</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2724150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FEEA120-8C8C-404B-AEED-1106826EE21C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1857375" y="38100"/>
+          <a:ext cx="866775" cy="685800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5375,84 +6025,84 @@
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="182" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="182"/>
+      <c r="A6" s="208" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="208"/>
+      <c r="C6" s="208"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="208"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="209" t="s">
         <v>341</v>
       </c>
-      <c r="B8" s="183"/>
-      <c r="C8" s="183"/>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="209"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="180"/>
-      <c r="B9" s="180"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="180"/>
-      <c r="E9" s="180"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="180"/>
-      <c r="H9" s="180"/>
+      <c r="A9" s="206"/>
+      <c r="B9" s="206"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
     </row>
     <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="182" t="s">
+      <c r="A10" s="208" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="182"/>
-      <c r="C10" s="182"/>
-      <c r="D10" s="182"/>
-      <c r="E10" s="182"/>
-      <c r="F10" s="182"/>
-      <c r="G10" s="182"/>
-      <c r="H10" s="182"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
+      <c r="D10" s="208"/>
+      <c r="E10" s="208"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
     </row>
     <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="181" t="s">
+      <c r="A11" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="179"/>
-      <c r="B12" s="179"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="179"/>
-      <c r="E12" s="179"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="179"/>
+      <c r="A12" s="205"/>
+      <c r="B12" s="205"/>
+      <c r="C12" s="205"/>
+      <c r="D12" s="205"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="205"/>
+      <c r="G12" s="205"/>
+      <c r="H12" s="205"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F13" s="43"/>
@@ -10102,76 +10752,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="184" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
+      <c r="A1" s="214" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
     </row>
     <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="185" t="s">
+      <c r="A3" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
     </row>
     <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="184">
+      <c r="A4" s="214">
         <f>'Detailed Financial Performance'!A9</f>
         <v>0</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="189" t="s">
+      <c r="A5" s="215" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="190" t="s">
+      <c r="A6" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="190"/>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="185">
+      <c r="A7" s="217">
         <f>'Detailed Financial Performance'!A12</f>
         <v>0</v>
       </c>
-      <c r="B7" s="185"/>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
@@ -10181,11 +10831,11 @@
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="185" t="s">
+      <c r="A9" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
+      <c r="B9" s="214"/>
+      <c r="C9" s="214"/>
       <c r="D9" s="2">
         <f>'Detailed Financial Performance'!F13</f>
         <v>0</v>
@@ -10194,11 +10844,11 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="191" t="s">
+      <c r="A10" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="191"/>
-      <c r="C10" s="191"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
       <c r="D10" s="5"/>
       <c r="E10" s="1"/>
     </row>
@@ -10264,10 +10914,10 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="186" t="s">
+      <c r="B16" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="186"/>
+      <c r="C16" s="212"/>
       <c r="D16" s="45">
         <f>'Detailed Financial Performance'!F118</f>
         <v>0</v>
@@ -10287,11 +10937,11 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="187" t="s">
+      <c r="A18" s="213" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="187"/>
-      <c r="C18" s="187"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="213"/>
       <c r="D18" s="46">
         <f>SUM(D11:D17)</f>
         <v>0</v>
@@ -10326,7 +10976,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="45">
-        <f>'Detailed Financial Performance'!F234</f>
+        <f>'Detailed Financial Performance'!F234+'Detailed Financial Performance'!F300+'Detailed Financial Performance'!F304</f>
         <v>0</v>
       </c>
       <c r="E21" s="9"/>
@@ -10356,11 +11006,11 @@
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A24" s="187" t="s">
+      <c r="A24" s="213" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="187"/>
-      <c r="C24" s="187"/>
+      <c r="B24" s="213"/>
+      <c r="C24" s="213"/>
       <c r="D24" s="47">
         <f>SUM(D20:D23)</f>
         <v>0</v>
@@ -10368,11 +11018,11 @@
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A25" s="188" t="s">
+      <c r="A25" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="188"/>
-      <c r="C25" s="188"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="210"/>
       <c r="D25" s="48">
         <f>D18-D24</f>
         <v>0</v>
@@ -10381,10 +11031,10 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="188" t="s">
+      <c r="B26" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="188"/>
+      <c r="C26" s="210"/>
       <c r="D26" s="45"/>
       <c r="E26" s="1"/>
     </row>
@@ -10406,18 +11056,15 @@
       <c r="C28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="49">
-        <f>'Detailed Financial Performance'!F300+'Detailed Financial Performance'!F304</f>
-        <v>0</v>
-      </c>
+      <c r="D28" s="49"/>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A29" s="192" t="s">
+      <c r="A29" s="211" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="192"/>
-      <c r="C29" s="192"/>
+      <c r="B29" s="211"/>
+      <c r="C29" s="211"/>
       <c r="D29" s="48">
         <f>D25+D27-D28</f>
         <v>0</v>
@@ -10432,10 +11079,10 @@
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="186" t="s">
+      <c r="A31" s="212" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="186"/>
+      <c r="B31" s="212"/>
       <c r="C31" s="13" t="s">
         <v>27</v>
       </c>
@@ -10451,8 +11098,8 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
-      <c r="B33" s="188"/>
-      <c r="C33" s="188"/>
+      <c r="B33" s="210"/>
+      <c r="C33" s="210"/>
       <c r="D33" s="14" t="s">
         <v>28</v>
       </c>
@@ -10460,8 +11107,8 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="186"/>
-      <c r="C34" s="186"/>
+      <c r="B34" s="212"/>
+      <c r="C34" s="212"/>
       <c r="D34" s="7" t="s">
         <v>29</v>
       </c>
@@ -10469,11 +11116,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
@@ -10482,11 +11129,11 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="76" orientation="portrait" r:id="rId1"/>
@@ -10516,91 +11163,91 @@
     <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="182" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
+      <c r="A5" s="208" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
     </row>
     <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="182"/>
-      <c r="I6" s="182"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="208"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
+      <c r="I6" s="208"/>
     </row>
     <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="183" t="s">
+      <c r="A7" s="209" t="s">
         <v>341</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
+      <c r="B7" s="209"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="209"/>
+      <c r="I7" s="209"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="179"/>
-      <c r="B8" s="179"/>
-      <c r="C8" s="179"/>
-      <c r="D8" s="179"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="179"/>
-      <c r="H8" s="179"/>
-      <c r="I8" s="179"/>
+      <c r="A8" s="205"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
     </row>
     <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="182" t="s">
+      <c r="A9" s="208" t="s">
         <v>342</v>
       </c>
-      <c r="B9" s="182"/>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="208"/>
     </row>
     <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="181" t="s">
+      <c r="A10" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="181"/>
-      <c r="C10" s="181"/>
-      <c r="D10" s="181"/>
-      <c r="E10" s="181"/>
-      <c r="F10" s="181"/>
-      <c r="G10" s="181"/>
-      <c r="H10" s="181"/>
-      <c r="I10" s="181"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="207"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="207"/>
     </row>
     <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="207"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F12" s="52"/>
@@ -19846,105 +20493,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="184" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="A1" s="214" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
     </row>
     <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="185" t="s">
+      <c r="A3" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="217"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
+      <c r="A4" s="214"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="189" t="s">
+      <c r="A5" s="215" t="s">
         <v>759</v>
       </c>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="215"/>
     </row>
     <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="185"/>
-      <c r="B6" s="185"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="185"/>
+      <c r="A6" s="217"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
     </row>
     <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="190" t="s">
+      <c r="A7" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="190"/>
-      <c r="C7" s="190"/>
-      <c r="D7" s="190"/>
-      <c r="E7" s="190"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="190"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
     </row>
     <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
+      <c r="A8" s="229"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
     </row>
     <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="195" t="s">
+      <c r="A9" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="195"/>
-      <c r="C9" s="196"/>
+      <c r="B9" s="230"/>
+      <c r="C9" s="231"/>
       <c r="D9" s="85"/>
       <c r="E9" s="85"/>
       <c r="F9" s="85"/>
       <c r="G9" s="85"/>
     </row>
     <row r="10" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="197" t="s">
+      <c r="A10" s="225" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-      <c r="D10" s="197"/>
+      <c r="B10" s="225"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
       <c r="I10" s="87"/>
     </row>
     <row r="11" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -20035,11 +20682,11 @@
       <c r="I16" s="87"/>
     </row>
     <row r="17" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="198" t="s">
+      <c r="A17" s="226" t="s">
         <v>765</v>
       </c>
-      <c r="B17" s="198"/>
-      <c r="C17" s="198"/>
+      <c r="B17" s="226"/>
+      <c r="C17" s="226"/>
       <c r="D17" s="95">
         <f>SUM(D12:D16)</f>
         <v>0</v>
@@ -20162,11 +20809,11 @@
       <c r="I25" s="87"/>
     </row>
     <row r="26" spans="1:9" s="86" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="193" t="s">
+      <c r="A26" s="228" t="s">
         <v>769</v>
       </c>
-      <c r="B26" s="193"/>
-      <c r="C26" s="193"/>
+      <c r="B26" s="228"/>
+      <c r="C26" s="228"/>
       <c r="D26" s="100">
         <f>SUM(D19:D24)</f>
         <v>0</v>
@@ -20177,11 +20824,11 @@
       <c r="I26" s="87"/>
     </row>
     <row r="27" spans="1:9" s="86" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="202" t="s">
+      <c r="A27" s="222" t="s">
         <v>770</v>
       </c>
-      <c r="B27" s="203"/>
-      <c r="C27" s="204"/>
+      <c r="B27" s="223"/>
+      <c r="C27" s="224"/>
       <c r="D27" s="101">
         <f>D17+D26</f>
         <v>0</v>
@@ -20192,12 +20839,12 @@
       <c r="I27" s="87"/>
     </row>
     <row r="28" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="197" t="s">
+      <c r="A28" s="225" t="s">
         <v>689</v>
       </c>
-      <c r="B28" s="197"/>
-      <c r="C28" s="197"/>
-      <c r="D28" s="197"/>
+      <c r="B28" s="225"/>
+      <c r="C28" s="225"/>
+      <c r="D28" s="225"/>
       <c r="E28" s="102"/>
       <c r="F28" s="102"/>
       <c r="G28" s="102"/>
@@ -20291,11 +20938,11 @@
       <c r="I34" s="87"/>
     </row>
     <row r="35" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="198" t="s">
+      <c r="A35" s="226" t="s">
         <v>748</v>
       </c>
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="226"/>
       <c r="D35" s="95">
         <f>SUM(D30:D34)</f>
         <v>0</v>
@@ -20378,11 +21025,11 @@
       <c r="I40" s="87"/>
     </row>
     <row r="41" spans="1:9" s="86" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="205" t="s">
+      <c r="A41" s="227" t="s">
         <v>774</v>
       </c>
-      <c r="B41" s="205"/>
-      <c r="C41" s="205"/>
+      <c r="B41" s="227"/>
+      <c r="C41" s="227"/>
       <c r="D41" s="104">
         <f>SUM(D37:D40)</f>
         <v>0</v>
@@ -20393,11 +21040,11 @@
       <c r="I41" s="87"/>
     </row>
     <row r="42" spans="1:9" s="86" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="202" t="s">
+      <c r="A42" s="222" t="s">
         <v>775</v>
       </c>
-      <c r="B42" s="203"/>
-      <c r="C42" s="204"/>
+      <c r="B42" s="223"/>
+      <c r="C42" s="224"/>
       <c r="D42" s="101">
         <f>SUM(D35+D41)</f>
         <v>0</v>
@@ -20408,12 +21055,12 @@
       <c r="I42" s="87"/>
     </row>
     <row r="43" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="197" t="s">
+      <c r="A43" s="225" t="s">
         <v>753</v>
       </c>
-      <c r="B43" s="197"/>
-      <c r="C43" s="197"/>
-      <c r="D43" s="197"/>
+      <c r="B43" s="225"/>
+      <c r="C43" s="225"/>
+      <c r="D43" s="225"/>
       <c r="E43" s="102"/>
       <c r="F43" s="102"/>
       <c r="G43" s="102"/>
@@ -20435,11 +21082,11 @@
       <c r="I44" s="87"/>
     </row>
     <row r="45" spans="1:9" s="86" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="199" t="s">
+      <c r="A45" s="219" t="s">
         <v>777</v>
       </c>
-      <c r="B45" s="200"/>
-      <c r="C45" s="201"/>
+      <c r="B45" s="220"/>
+      <c r="C45" s="221"/>
       <c r="D45" s="105">
         <f>D42+D44</f>
         <v>0</v>
@@ -20467,11 +21114,11 @@
         <v>26</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="D48" s="186" t="s">
+      <c r="D48" s="212" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186"/>
+      <c r="E48" s="212"/>
+      <c r="F48" s="212"/>
       <c r="G48" s="109"/>
       <c r="I48" s="111"/>
     </row>
@@ -20487,8 +21134,8 @@
     </row>
     <row r="50" spans="1:9" s="110" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
-      <c r="B50" s="188"/>
-      <c r="C50" s="188"/>
+      <c r="B50" s="210"/>
+      <c r="C50" s="210"/>
       <c r="E50" s="14" t="s">
         <v>28</v>
       </c>
@@ -20498,8 +21145,8 @@
     </row>
     <row r="51" spans="1:9" s="110" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
-      <c r="B51" s="186"/>
-      <c r="C51" s="186"/>
+      <c r="B51" s="212"/>
+      <c r="C51" s="212"/>
       <c r="E51" s="7" t="s">
         <v>29</v>
       </c>
@@ -20509,16 +21156,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -20531,6 +21168,16 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:D43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" orientation="portrait" r:id="rId1"/>
@@ -21188,101 +21835,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="230" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
+      <c r="A1" s="233" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
     </row>
     <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="230" t="s">
+      <c r="A2" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="230"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="231"/>
-      <c r="I3" s="231"/>
+      <c r="B3" s="234"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="234"/>
+      <c r="I3" s="234"/>
     </row>
     <row r="4" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="230"/>
-      <c r="B4" s="230"/>
-      <c r="C4" s="230"/>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
+      <c r="A4" s="233"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="232" t="s">
+      <c r="A5" s="235" t="s">
         <v>778</v>
       </c>
-      <c r="B5" s="232"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
+      <c r="B5" s="235"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
     </row>
     <row r="6" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="232" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="229"/>
-      <c r="C6" s="229"/>
-      <c r="D6" s="229"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="229"/>
-      <c r="I6" s="229"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="221"/>
-      <c r="B7" s="221"/>
-      <c r="C7" s="221"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="221"/>
-      <c r="H7" s="221"/>
-      <c r="I7" s="221"/>
+      <c r="A7" s="237"/>
+      <c r="B7" s="237"/>
+      <c r="C7" s="237"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="237"/>
+      <c r="H7" s="237"/>
+      <c r="I7" s="237"/>
       <c r="L7" s="113"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="222" t="s">
+      <c r="A8" s="238" t="s">
         <v>779</v>
       </c>
-      <c r="B8" s="223"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="224"/>
+      <c r="B8" s="239"/>
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="240"/>
       <c r="F8" s="114"/>
       <c r="G8" s="115"/>
       <c r="H8" s="114"/>
@@ -21318,12 +21965,12 @@
     </row>
     <row r="11" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="121"/>
-      <c r="B11" s="225" t="s">
+      <c r="B11" s="241" t="s">
         <v>782</v>
       </c>
-      <c r="C11" s="225"/>
-      <c r="D11" s="225"/>
-      <c r="E11" s="226"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="242"/>
       <c r="F11" s="118">
         <f>'Condensed Financial Performance'!D11</f>
         <v>0</v>
@@ -21337,12 +21984,12 @@
     </row>
     <row r="12" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="121"/>
-      <c r="B12" s="225" t="s">
+      <c r="B12" s="241" t="s">
         <v>783</v>
       </c>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="226"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="241"/>
+      <c r="E12" s="242"/>
       <c r="F12" s="118">
         <f>'Condensed Financial Performance'!D12</f>
         <v>0</v>
@@ -21356,12 +22003,12 @@
     </row>
     <row r="13" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="121"/>
-      <c r="B13" s="225" t="s">
+      <c r="B13" s="241" t="s">
         <v>784</v>
       </c>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="226"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="242"/>
       <c r="F13" s="118">
         <f>'Condensed Financial Performance'!D14</f>
         <v>0</v>
@@ -21375,12 +22022,12 @@
     </row>
     <row r="14" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="121"/>
-      <c r="B14" s="225" t="s">
+      <c r="B14" s="241" t="s">
         <v>785</v>
       </c>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="226"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="241"/>
+      <c r="E14" s="242"/>
       <c r="F14" s="118"/>
       <c r="G14" s="120"/>
       <c r="H14" s="118"/>
@@ -21391,12 +22038,12 @@
     </row>
     <row r="15" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="121"/>
-      <c r="B15" s="225" t="s">
+      <c r="B15" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="226"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="241"/>
+      <c r="E15" s="242"/>
       <c r="F15" s="118"/>
       <c r="G15" s="120"/>
       <c r="H15" s="118"/>
@@ -21407,12 +22054,12 @@
     </row>
     <row r="16" spans="1:12" s="125" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121"/>
-      <c r="B16" s="225" t="s">
+      <c r="B16" s="241" t="s">
         <v>786</v>
       </c>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="226"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="242"/>
       <c r="F16" s="118"/>
       <c r="G16" s="127"/>
       <c r="H16" s="118"/>
@@ -21423,12 +22070,12 @@
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="121"/>
-      <c r="B17" s="227" t="s">
+      <c r="B17" s="243" t="s">
         <v>787</v>
       </c>
-      <c r="C17" s="227"/>
-      <c r="D17" s="227"/>
-      <c r="E17" s="228"/>
+      <c r="C17" s="243"/>
+      <c r="D17" s="243"/>
+      <c r="E17" s="244"/>
       <c r="F17" s="128">
         <f>SUM(F11:F16)</f>
         <v>0</v>
@@ -21458,12 +22105,12 @@
     </row>
     <row r="19" spans="1:13" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="121"/>
-      <c r="B19" s="207" t="s">
+      <c r="B19" s="236" t="s">
         <v>789</v>
       </c>
-      <c r="C19" s="207"/>
-      <c r="D19" s="207"/>
-      <c r="E19" s="208"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="236"/>
+      <c r="E19" s="245"/>
       <c r="F19"/>
       <c r="G19" s="120"/>
       <c r="H19" s="118"/>
@@ -21474,12 +22121,12 @@
     </row>
     <row r="20" spans="1:13" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="121"/>
-      <c r="B20" s="207" t="s">
+      <c r="B20" s="236" t="s">
         <v>790</v>
       </c>
-      <c r="C20" s="207"/>
-      <c r="D20" s="207"/>
-      <c r="E20" s="208"/>
+      <c r="C20" s="236"/>
+      <c r="D20" s="236"/>
+      <c r="E20" s="245"/>
       <c r="F20"/>
       <c r="G20" s="120"/>
       <c r="H20" s="118"/>
@@ -21490,12 +22137,12 @@
     </row>
     <row r="21" spans="1:13" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="121"/>
-      <c r="B21" s="207" t="s">
+      <c r="B21" s="236" t="s">
         <v>791</v>
       </c>
-      <c r="C21" s="207"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="236"/>
+      <c r="E21" s="236"/>
       <c r="F21" s="163">
         <f>'Condensed Financial Performance'!D20</f>
         <v>0</v>
@@ -21509,12 +22156,12 @@
     </row>
     <row r="22" spans="1:13" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="121"/>
-      <c r="B22" s="207" t="s">
+      <c r="B22" s="236" t="s">
         <v>792</v>
       </c>
-      <c r="C22" s="207"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
+      <c r="C22" s="236"/>
+      <c r="D22" s="236"/>
+      <c r="E22" s="236"/>
       <c r="F22" s="163">
         <f>'Condensed Financial Performance'!D21</f>
         <v>0</v>
@@ -21528,12 +22175,12 @@
     </row>
     <row r="23" spans="1:13" s="125" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="121"/>
-      <c r="B23" s="207" t="s">
+      <c r="B23" s="236" t="s">
         <v>793</v>
       </c>
-      <c r="C23" s="207"/>
-      <c r="D23" s="207"/>
-      <c r="E23" s="207"/>
+      <c r="C23" s="236"/>
+      <c r="D23" s="236"/>
+      <c r="E23" s="236"/>
       <c r="F23" s="118">
         <f>'Condensed Financial Performance'!D22</f>
         <v>0</v>
@@ -21547,12 +22194,12 @@
     </row>
     <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="121"/>
-      <c r="B24" s="209" t="s">
+      <c r="B24" s="246" t="s">
         <v>794</v>
       </c>
-      <c r="C24" s="209"/>
-      <c r="D24" s="209"/>
-      <c r="E24" s="209"/>
+      <c r="C24" s="246"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="246"/>
       <c r="F24" s="132">
         <f>SUM(F20:F23)</f>
         <v>0</v>
@@ -21618,12 +22265,12 @@
     </row>
     <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="121"/>
-      <c r="B28" s="207" t="s">
+      <c r="B28" s="236" t="s">
         <v>797</v>
       </c>
-      <c r="C28" s="207"/>
-      <c r="D28" s="207"/>
-      <c r="E28" s="208"/>
+      <c r="C28" s="236"/>
+      <c r="D28" s="236"/>
+      <c r="E28" s="245"/>
       <c r="F28" s="118"/>
       <c r="G28" s="120"/>
       <c r="H28" s="118"/>
@@ -21634,12 +22281,12 @@
     </row>
     <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="121"/>
-      <c r="B29" s="207" t="s">
+      <c r="B29" s="236" t="s">
         <v>798</v>
       </c>
-      <c r="C29" s="207"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="208"/>
+      <c r="C29" s="236"/>
+      <c r="D29" s="236"/>
+      <c r="E29" s="245"/>
       <c r="F29" s="118"/>
       <c r="G29" s="120"/>
       <c r="H29" s="118"/>
@@ -21650,12 +22297,12 @@
     </row>
     <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="121"/>
-      <c r="B30" s="207" t="s">
+      <c r="B30" s="236" t="s">
         <v>799</v>
       </c>
-      <c r="C30" s="207"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="208"/>
+      <c r="C30" s="236"/>
+      <c r="D30" s="236"/>
+      <c r="E30" s="245"/>
       <c r="F30" s="118"/>
       <c r="G30" s="120"/>
       <c r="H30" s="118"/>
@@ -21666,12 +22313,12 @@
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="121"/>
-      <c r="B31" s="207" t="s">
+      <c r="B31" s="236" t="s">
         <v>800</v>
       </c>
-      <c r="C31" s="207"/>
-      <c r="D31" s="207"/>
-      <c r="E31" s="208"/>
+      <c r="C31" s="236"/>
+      <c r="D31" s="236"/>
+      <c r="E31" s="245"/>
       <c r="F31" s="118"/>
       <c r="G31" s="120"/>
       <c r="H31" s="118"/>
@@ -21682,12 +22329,12 @@
     </row>
     <row r="32" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="121"/>
-      <c r="B32" s="209" t="s">
+      <c r="B32" s="246" t="s">
         <v>787</v>
       </c>
-      <c r="C32" s="209"/>
-      <c r="D32" s="209"/>
-      <c r="E32" s="210"/>
+      <c r="C32" s="246"/>
+      <c r="D32" s="246"/>
+      <c r="E32" s="247"/>
       <c r="F32" s="128">
         <f>SUM(F28:F31)</f>
         <v>0</v>
@@ -21717,16 +22364,13 @@
     </row>
     <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="121"/>
-      <c r="B34" s="207" t="s">
+      <c r="B34" s="236" t="s">
         <v>801</v>
       </c>
-      <c r="C34" s="207"/>
-      <c r="D34" s="207"/>
-      <c r="E34" s="208"/>
-      <c r="F34" s="118">
-        <f>'Financial Position'!D21</f>
-        <v>0</v>
-      </c>
+      <c r="C34" s="236"/>
+      <c r="D34" s="236"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="118"/>
       <c r="G34" s="120"/>
       <c r="H34" s="118"/>
       <c r="I34" s="118"/>
@@ -21736,14 +22380,14 @@
     </row>
     <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="121"/>
-      <c r="B35" s="207" t="s">
+      <c r="B35" s="236" t="s">
         <v>802</v>
       </c>
-      <c r="C35" s="207"/>
-      <c r="D35" s="207"/>
-      <c r="E35" s="208"/>
+      <c r="C35" s="236"/>
+      <c r="D35" s="236"/>
+      <c r="E35" s="245"/>
       <c r="F35" s="118">
-        <f>'Financial Position'!D22</f>
+        <f>SUM(TB!E27:E80)+TB!E19+TB!E85</f>
         <v>0</v>
       </c>
       <c r="G35" s="120"/>
@@ -21755,12 +22399,12 @@
     </row>
     <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="121"/>
-      <c r="B36" s="207" t="s">
+      <c r="B36" s="236" t="s">
         <v>803</v>
       </c>
-      <c r="C36" s="207"/>
-      <c r="D36" s="207"/>
-      <c r="E36" s="208"/>
+      <c r="C36" s="236"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="245"/>
       <c r="F36" s="118"/>
       <c r="G36" s="120"/>
       <c r="H36" s="118"/>
@@ -21771,12 +22415,12 @@
     </row>
     <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="121"/>
-      <c r="B37" s="207" t="s">
+      <c r="B37" s="236" t="s">
         <v>804</v>
       </c>
-      <c r="C37" s="207"/>
-      <c r="D37" s="207"/>
-      <c r="E37" s="208"/>
+      <c r="C37" s="236"/>
+      <c r="D37" s="236"/>
+      <c r="E37" s="245"/>
       <c r="F37" s="118"/>
       <c r="G37" s="120"/>
       <c r="H37" s="118"/>
@@ -21787,12 +22431,12 @@
     </row>
     <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="121"/>
-      <c r="B38" s="207" t="s">
+      <c r="B38" s="236" t="s">
         <v>805</v>
       </c>
-      <c r="C38" s="207"/>
-      <c r="D38" s="207"/>
-      <c r="E38" s="208"/>
+      <c r="C38" s="236"/>
+      <c r="D38" s="236"/>
+      <c r="E38" s="245"/>
       <c r="F38" s="118"/>
       <c r="G38" s="120"/>
       <c r="H38" s="118"/>
@@ -21803,12 +22447,12 @@
     </row>
     <row r="39" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="121"/>
-      <c r="B39" s="207" t="s">
+      <c r="B39" s="236" t="s">
         <v>806</v>
       </c>
-      <c r="C39" s="207"/>
-      <c r="D39" s="207"/>
-      <c r="E39" s="208"/>
+      <c r="C39" s="236"/>
+      <c r="D39" s="236"/>
+      <c r="E39" s="245"/>
       <c r="F39" s="118"/>
       <c r="G39" s="120"/>
       <c r="H39" s="118"/>
@@ -21819,12 +22463,12 @@
     </row>
     <row r="40" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="121"/>
-      <c r="B40" s="209" t="s">
+      <c r="B40" s="246" t="s">
         <v>794</v>
       </c>
-      <c r="C40" s="209"/>
-      <c r="D40" s="209"/>
-      <c r="E40" s="210"/>
+      <c r="C40" s="246"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="247"/>
       <c r="F40" s="128">
         <f>SUM(F34:F39)</f>
         <v>0</v>
@@ -21885,12 +22529,12 @@
     </row>
     <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="121"/>
-      <c r="B44" s="207" t="s">
+      <c r="B44" s="236" t="s">
         <v>809</v>
       </c>
-      <c r="C44" s="207"/>
-      <c r="D44" s="207"/>
-      <c r="E44" s="208"/>
+      <c r="C44" s="236"/>
+      <c r="D44" s="236"/>
+      <c r="E44" s="245"/>
       <c r="F44" s="118"/>
       <c r="G44" s="120"/>
       <c r="H44" s="118"/>
@@ -21900,12 +22544,12 @@
     </row>
     <row r="45" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="121"/>
-      <c r="B45" s="207" t="s">
+      <c r="B45" s="236" t="s">
         <v>810</v>
       </c>
-      <c r="C45" s="207"/>
-      <c r="D45" s="207"/>
-      <c r="E45" s="208"/>
+      <c r="C45" s="236"/>
+      <c r="D45" s="236"/>
+      <c r="E45" s="245"/>
       <c r="F45" s="118"/>
       <c r="G45" s="120"/>
       <c r="H45" s="118"/>
@@ -21915,12 +22559,12 @@
     </row>
     <row r="46" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="121"/>
-      <c r="B46" s="209" t="s">
+      <c r="B46" s="246" t="s">
         <v>787</v>
       </c>
-      <c r="C46" s="209"/>
-      <c r="D46" s="209"/>
-      <c r="E46" s="210"/>
+      <c r="C46" s="246"/>
+      <c r="D46" s="246"/>
+      <c r="E46" s="247"/>
       <c r="F46" s="128">
         <f>F44+F45</f>
         <v>0</v>
@@ -21948,12 +22592,12 @@
     </row>
     <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="116"/>
-      <c r="B48" s="207" t="s">
+      <c r="B48" s="236" t="s">
         <v>811</v>
       </c>
-      <c r="C48" s="207"/>
-      <c r="D48" s="207"/>
-      <c r="E48" s="208"/>
+      <c r="C48" s="236"/>
+      <c r="D48" s="236"/>
+      <c r="E48" s="245"/>
       <c r="G48" s="120"/>
       <c r="H48" s="118"/>
       <c r="I48" s="118"/>
@@ -21962,12 +22606,12 @@
     </row>
     <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="121"/>
-      <c r="B49" s="207" t="s">
+      <c r="B49" s="236" t="s">
         <v>812</v>
       </c>
-      <c r="C49" s="207"/>
-      <c r="D49" s="207"/>
-      <c r="E49" s="208"/>
+      <c r="C49" s="236"/>
+      <c r="D49" s="236"/>
+      <c r="E49" s="245"/>
       <c r="F49" s="118"/>
       <c r="G49" s="120"/>
       <c r="H49" s="118"/>
@@ -21977,12 +22621,12 @@
     </row>
     <row r="50" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="121"/>
-      <c r="B50" s="207" t="s">
+      <c r="B50" s="236" t="s">
         <v>813</v>
       </c>
-      <c r="C50" s="207"/>
-      <c r="D50" s="207"/>
-      <c r="E50" s="208"/>
+      <c r="C50" s="236"/>
+      <c r="D50" s="236"/>
+      <c r="E50" s="245"/>
       <c r="F50" s="118"/>
       <c r="G50" s="120"/>
       <c r="H50" s="118"/>
@@ -21992,12 +22636,12 @@
     </row>
     <row r="51" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="121"/>
-      <c r="B51" s="209" t="s">
+      <c r="B51" s="246" t="s">
         <v>794</v>
       </c>
-      <c r="C51" s="209"/>
-      <c r="D51" s="209"/>
-      <c r="E51" s="210"/>
+      <c r="C51" s="246"/>
+      <c r="D51" s="246"/>
+      <c r="E51" s="247"/>
       <c r="F51" s="128">
         <f>SUM(F48:F50)</f>
         <v>0</v>
@@ -22008,8 +22652,8 @@
       <c r="J51" s="110"/>
       <c r="K51" s="110"/>
       <c r="M51" s="148"/>
-      <c r="N51" s="218"/>
-      <c r="O51" s="219"/>
+      <c r="N51" s="248"/>
+      <c r="O51" s="249"/>
     </row>
     <row r="52" spans="1:15" s="143" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="134" t="s">
@@ -22028,17 +22672,17 @@
       <c r="I52" s="145"/>
       <c r="J52" s="139"/>
       <c r="K52" s="139"/>
-      <c r="N52" s="220"/>
-      <c r="O52" s="220"/>
+      <c r="N52" s="250"/>
+      <c r="O52" s="250"/>
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="211" t="s">
+      <c r="A53" s="252" t="s">
         <v>815</v>
       </c>
-      <c r="B53" s="212"/>
-      <c r="C53" s="212"/>
-      <c r="D53" s="212"/>
-      <c r="E53" s="213"/>
+      <c r="B53" s="253"/>
+      <c r="C53" s="253"/>
+      <c r="D53" s="253"/>
+      <c r="E53" s="254"/>
       <c r="F53" s="150">
         <f>F25+F41</f>
         <v>0</v>
@@ -22051,14 +22695,17 @@
       <c r="M53" s="113"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="211" t="s">
+      <c r="A54" s="252" t="s">
         <v>816</v>
       </c>
-      <c r="B54" s="212"/>
-      <c r="C54" s="212"/>
-      <c r="D54" s="212"/>
-      <c r="E54" s="213"/>
-      <c r="F54" s="152"/>
+      <c r="B54" s="253"/>
+      <c r="C54" s="253"/>
+      <c r="D54" s="253"/>
+      <c r="E54" s="254"/>
+      <c r="F54" s="152">
+        <f>'Detailed Financial Position'!F553</f>
+        <v>0</v>
+      </c>
       <c r="G54" s="144"/>
       <c r="H54" s="152"/>
       <c r="I54" s="152"/>
@@ -22067,13 +22714,13 @@
       <c r="M54" s="113"/>
     </row>
     <row r="55" spans="1:15" s="156" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="214" t="s">
+      <c r="A55" s="255" t="s">
         <v>817</v>
       </c>
-      <c r="B55" s="215"/>
-      <c r="C55" s="215"/>
-      <c r="D55" s="215"/>
-      <c r="E55" s="216"/>
+      <c r="B55" s="256"/>
+      <c r="C55" s="256"/>
+      <c r="D55" s="256"/>
+      <c r="E55" s="257"/>
       <c r="F55" s="153">
         <f>F53+F54</f>
         <v>0</v>
@@ -22107,15 +22754,15 @@
       <c r="I58" s="160"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="187"/>
-      <c r="B59" s="187"/>
-      <c r="C59" s="187"/>
-      <c r="D59" s="187"/>
-      <c r="E59" s="217" t="s">
+      <c r="A59" s="213"/>
+      <c r="B59" s="213"/>
+      <c r="C59" s="213"/>
+      <c r="D59" s="213"/>
+      <c r="E59" s="258" t="s">
         <v>819</v>
       </c>
-      <c r="F59" s="187"/>
-      <c r="G59" s="187"/>
+      <c r="F59" s="213"/>
+      <c r="G59" s="213"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="L59" s="113"/>
@@ -22123,15 +22770,15 @@
       <c r="N59" s="113"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="206"/>
-      <c r="B60" s="206"/>
-      <c r="C60" s="206"/>
-      <c r="D60" s="206"/>
-      <c r="E60" s="206" t="s">
+      <c r="A60" s="251"/>
+      <c r="B60" s="251"/>
+      <c r="C60" s="251"/>
+      <c r="D60" s="251"/>
+      <c r="E60" s="251" t="s">
         <v>29</v>
       </c>
-      <c r="F60" s="206"/>
-      <c r="G60" s="206"/>
+      <c r="F60" s="251"/>
+      <c r="G60" s="251"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="L60" s="113"/>
@@ -22153,12 +22800,37 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:E8"/>
@@ -22171,37 +22843,12 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
@@ -22227,90 +22874,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="233" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
+      <c r="A1" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="259"/>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
+      <c r="J1" s="259"/>
+      <c r="K1" s="259"/>
     </row>
     <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A2" s="237" t="s">
+      <c r="A2" s="263" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="237"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="237"/>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
+      <c r="B2" s="263"/>
+      <c r="C2" s="263"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="263"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
     </row>
     <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="237" t="s">
+      <c r="A3" s="263" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
+      <c r="B3" s="263"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="263"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="233"/>
-      <c r="B4" s="233"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
+      <c r="A4" s="259"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="238" t="s">
+      <c r="A5" s="264" t="s">
         <v>820</v>
       </c>
-      <c r="B5" s="238"/>
-      <c r="C5" s="238"/>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
+      <c r="B5" s="264"/>
+      <c r="C5" s="264"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="237"/>
-      <c r="B6" s="237"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="237"/>
-      <c r="F6" s="237"/>
-      <c r="G6" s="237"/>
-      <c r="H6" s="237"/>
-      <c r="I6" s="237"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="237"/>
+      <c r="A6" s="263"/>
+      <c r="B6" s="263"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="263"/>
+      <c r="E6" s="263"/>
+      <c r="F6" s="263"/>
+      <c r="G6" s="263"/>
+      <c r="H6" s="263"/>
+      <c r="I6" s="263"/>
+      <c r="J6" s="263"/>
+      <c r="K6" s="263"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="165"/>
@@ -22323,18 +22970,18 @@
       <c r="H8" s="165"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H9" s="234" t="s">
+      <c r="H9" s="260" t="s">
         <v>821</v>
       </c>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H10" s="234" t="s">
+      <c r="H10" s="260" t="s">
         <v>822</v>
       </c>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H11" s="167"/>
@@ -22348,11 +22995,11 @@
       <c r="H13" s="166"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="236"/>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="236"/>
-      <c r="E14" s="236"/>
+      <c r="A14" s="262"/>
+      <c r="B14" s="262"/>
+      <c r="C14" s="262"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
       <c r="H14" s="170">
         <f>'Detailed Financial Position'!F553</f>
         <v>0</v>
@@ -22430,11 +23077,11 @@
       <c r="H23" s="170"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="236"/>
-      <c r="B24" s="236"/>
-      <c r="C24" s="236"/>
-      <c r="D24" s="236"/>
-      <c r="E24" s="236"/>
+      <c r="A24" s="262"/>
+      <c r="B24" s="262"/>
+      <c r="C24" s="262"/>
+      <c r="D24" s="262"/>
+      <c r="E24" s="262"/>
       <c r="H24" s="175">
         <f>H18+H22</f>
         <v>0</v>
@@ -22461,24 +23108,24 @@
       <c r="H28" s="178"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="234"/>
-      <c r="B30" s="234"/>
-      <c r="C30" s="234"/>
-      <c r="F30" s="234" t="s">
+      <c r="A30" s="260"/>
+      <c r="B30" s="260"/>
+      <c r="C30" s="260"/>
+      <c r="F30" s="260" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="234"/>
-      <c r="H30" s="234"/>
+      <c r="G30" s="260"/>
+      <c r="H30" s="260"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="235"/>
-      <c r="B31" s="235"/>
-      <c r="C31" s="235"/>
-      <c r="F31" s="235" t="s">
+      <c r="A31" s="261"/>
+      <c r="B31" s="261"/>
+      <c r="C31" s="261"/>
+      <c r="F31" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="235"/>
-      <c r="H31" s="235"/>
+      <c r="G31" s="261"/>
+      <c r="H31" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -22501,4 +23148,2706 @@
   <pageSetup scale="70" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF8FD7B-E352-45EB-9183-EA550FF7A0AF}">
+  <dimension ref="A1:E216"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="64.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="257" max="257" width="64.85546875" customWidth="1"/>
+    <col min="258" max="258" width="12.5703125" customWidth="1"/>
+    <col min="259" max="259" width="16.5703125" customWidth="1"/>
+    <col min="260" max="260" width="16.85546875" customWidth="1"/>
+    <col min="261" max="261" width="13.85546875" customWidth="1"/>
+    <col min="513" max="513" width="64.85546875" customWidth="1"/>
+    <col min="514" max="514" width="12.5703125" customWidth="1"/>
+    <col min="515" max="515" width="16.5703125" customWidth="1"/>
+    <col min="516" max="516" width="16.85546875" customWidth="1"/>
+    <col min="517" max="517" width="13.85546875" customWidth="1"/>
+    <col min="769" max="769" width="64.85546875" customWidth="1"/>
+    <col min="770" max="770" width="12.5703125" customWidth="1"/>
+    <col min="771" max="771" width="16.5703125" customWidth="1"/>
+    <col min="772" max="772" width="16.85546875" customWidth="1"/>
+    <col min="773" max="773" width="13.85546875" customWidth="1"/>
+    <col min="1025" max="1025" width="64.85546875" customWidth="1"/>
+    <col min="1026" max="1026" width="12.5703125" customWidth="1"/>
+    <col min="1027" max="1027" width="16.5703125" customWidth="1"/>
+    <col min="1028" max="1028" width="16.85546875" customWidth="1"/>
+    <col min="1029" max="1029" width="13.85546875" customWidth="1"/>
+    <col min="1281" max="1281" width="64.85546875" customWidth="1"/>
+    <col min="1282" max="1282" width="12.5703125" customWidth="1"/>
+    <col min="1283" max="1283" width="16.5703125" customWidth="1"/>
+    <col min="1284" max="1284" width="16.85546875" customWidth="1"/>
+    <col min="1285" max="1285" width="13.85546875" customWidth="1"/>
+    <col min="1537" max="1537" width="64.85546875" customWidth="1"/>
+    <col min="1538" max="1538" width="12.5703125" customWidth="1"/>
+    <col min="1539" max="1539" width="16.5703125" customWidth="1"/>
+    <col min="1540" max="1540" width="16.85546875" customWidth="1"/>
+    <col min="1541" max="1541" width="13.85546875" customWidth="1"/>
+    <col min="1793" max="1793" width="64.85546875" customWidth="1"/>
+    <col min="1794" max="1794" width="12.5703125" customWidth="1"/>
+    <col min="1795" max="1795" width="16.5703125" customWidth="1"/>
+    <col min="1796" max="1796" width="16.85546875" customWidth="1"/>
+    <col min="1797" max="1797" width="13.85546875" customWidth="1"/>
+    <col min="2049" max="2049" width="64.85546875" customWidth="1"/>
+    <col min="2050" max="2050" width="12.5703125" customWidth="1"/>
+    <col min="2051" max="2051" width="16.5703125" customWidth="1"/>
+    <col min="2052" max="2052" width="16.85546875" customWidth="1"/>
+    <col min="2053" max="2053" width="13.85546875" customWidth="1"/>
+    <col min="2305" max="2305" width="64.85546875" customWidth="1"/>
+    <col min="2306" max="2306" width="12.5703125" customWidth="1"/>
+    <col min="2307" max="2307" width="16.5703125" customWidth="1"/>
+    <col min="2308" max="2308" width="16.85546875" customWidth="1"/>
+    <col min="2309" max="2309" width="13.85546875" customWidth="1"/>
+    <col min="2561" max="2561" width="64.85546875" customWidth="1"/>
+    <col min="2562" max="2562" width="12.5703125" customWidth="1"/>
+    <col min="2563" max="2563" width="16.5703125" customWidth="1"/>
+    <col min="2564" max="2564" width="16.85546875" customWidth="1"/>
+    <col min="2565" max="2565" width="13.85546875" customWidth="1"/>
+    <col min="2817" max="2817" width="64.85546875" customWidth="1"/>
+    <col min="2818" max="2818" width="12.5703125" customWidth="1"/>
+    <col min="2819" max="2819" width="16.5703125" customWidth="1"/>
+    <col min="2820" max="2820" width="16.85546875" customWidth="1"/>
+    <col min="2821" max="2821" width="13.85546875" customWidth="1"/>
+    <col min="3073" max="3073" width="64.85546875" customWidth="1"/>
+    <col min="3074" max="3074" width="12.5703125" customWidth="1"/>
+    <col min="3075" max="3075" width="16.5703125" customWidth="1"/>
+    <col min="3076" max="3076" width="16.85546875" customWidth="1"/>
+    <col min="3077" max="3077" width="13.85546875" customWidth="1"/>
+    <col min="3329" max="3329" width="64.85546875" customWidth="1"/>
+    <col min="3330" max="3330" width="12.5703125" customWidth="1"/>
+    <col min="3331" max="3331" width="16.5703125" customWidth="1"/>
+    <col min="3332" max="3332" width="16.85546875" customWidth="1"/>
+    <col min="3333" max="3333" width="13.85546875" customWidth="1"/>
+    <col min="3585" max="3585" width="64.85546875" customWidth="1"/>
+    <col min="3586" max="3586" width="12.5703125" customWidth="1"/>
+    <col min="3587" max="3587" width="16.5703125" customWidth="1"/>
+    <col min="3588" max="3588" width="16.85546875" customWidth="1"/>
+    <col min="3589" max="3589" width="13.85546875" customWidth="1"/>
+    <col min="3841" max="3841" width="64.85546875" customWidth="1"/>
+    <col min="3842" max="3842" width="12.5703125" customWidth="1"/>
+    <col min="3843" max="3843" width="16.5703125" customWidth="1"/>
+    <col min="3844" max="3844" width="16.85546875" customWidth="1"/>
+    <col min="3845" max="3845" width="13.85546875" customWidth="1"/>
+    <col min="4097" max="4097" width="64.85546875" customWidth="1"/>
+    <col min="4098" max="4098" width="12.5703125" customWidth="1"/>
+    <col min="4099" max="4099" width="16.5703125" customWidth="1"/>
+    <col min="4100" max="4100" width="16.85546875" customWidth="1"/>
+    <col min="4101" max="4101" width="13.85546875" customWidth="1"/>
+    <col min="4353" max="4353" width="64.85546875" customWidth="1"/>
+    <col min="4354" max="4354" width="12.5703125" customWidth="1"/>
+    <col min="4355" max="4355" width="16.5703125" customWidth="1"/>
+    <col min="4356" max="4356" width="16.85546875" customWidth="1"/>
+    <col min="4357" max="4357" width="13.85546875" customWidth="1"/>
+    <col min="4609" max="4609" width="64.85546875" customWidth="1"/>
+    <col min="4610" max="4610" width="12.5703125" customWidth="1"/>
+    <col min="4611" max="4611" width="16.5703125" customWidth="1"/>
+    <col min="4612" max="4612" width="16.85546875" customWidth="1"/>
+    <col min="4613" max="4613" width="13.85546875" customWidth="1"/>
+    <col min="4865" max="4865" width="64.85546875" customWidth="1"/>
+    <col min="4866" max="4866" width="12.5703125" customWidth="1"/>
+    <col min="4867" max="4867" width="16.5703125" customWidth="1"/>
+    <col min="4868" max="4868" width="16.85546875" customWidth="1"/>
+    <col min="4869" max="4869" width="13.85546875" customWidth="1"/>
+    <col min="5121" max="5121" width="64.85546875" customWidth="1"/>
+    <col min="5122" max="5122" width="12.5703125" customWidth="1"/>
+    <col min="5123" max="5123" width="16.5703125" customWidth="1"/>
+    <col min="5124" max="5124" width="16.85546875" customWidth="1"/>
+    <col min="5125" max="5125" width="13.85546875" customWidth="1"/>
+    <col min="5377" max="5377" width="64.85546875" customWidth="1"/>
+    <col min="5378" max="5378" width="12.5703125" customWidth="1"/>
+    <col min="5379" max="5379" width="16.5703125" customWidth="1"/>
+    <col min="5380" max="5380" width="16.85546875" customWidth="1"/>
+    <col min="5381" max="5381" width="13.85546875" customWidth="1"/>
+    <col min="5633" max="5633" width="64.85546875" customWidth="1"/>
+    <col min="5634" max="5634" width="12.5703125" customWidth="1"/>
+    <col min="5635" max="5635" width="16.5703125" customWidth="1"/>
+    <col min="5636" max="5636" width="16.85546875" customWidth="1"/>
+    <col min="5637" max="5637" width="13.85546875" customWidth="1"/>
+    <col min="5889" max="5889" width="64.85546875" customWidth="1"/>
+    <col min="5890" max="5890" width="12.5703125" customWidth="1"/>
+    <col min="5891" max="5891" width="16.5703125" customWidth="1"/>
+    <col min="5892" max="5892" width="16.85546875" customWidth="1"/>
+    <col min="5893" max="5893" width="13.85546875" customWidth="1"/>
+    <col min="6145" max="6145" width="64.85546875" customWidth="1"/>
+    <col min="6146" max="6146" width="12.5703125" customWidth="1"/>
+    <col min="6147" max="6147" width="16.5703125" customWidth="1"/>
+    <col min="6148" max="6148" width="16.85546875" customWidth="1"/>
+    <col min="6149" max="6149" width="13.85546875" customWidth="1"/>
+    <col min="6401" max="6401" width="64.85546875" customWidth="1"/>
+    <col min="6402" max="6402" width="12.5703125" customWidth="1"/>
+    <col min="6403" max="6403" width="16.5703125" customWidth="1"/>
+    <col min="6404" max="6404" width="16.85546875" customWidth="1"/>
+    <col min="6405" max="6405" width="13.85546875" customWidth="1"/>
+    <col min="6657" max="6657" width="64.85546875" customWidth="1"/>
+    <col min="6658" max="6658" width="12.5703125" customWidth="1"/>
+    <col min="6659" max="6659" width="16.5703125" customWidth="1"/>
+    <col min="6660" max="6660" width="16.85546875" customWidth="1"/>
+    <col min="6661" max="6661" width="13.85546875" customWidth="1"/>
+    <col min="6913" max="6913" width="64.85546875" customWidth="1"/>
+    <col min="6914" max="6914" width="12.5703125" customWidth="1"/>
+    <col min="6915" max="6915" width="16.5703125" customWidth="1"/>
+    <col min="6916" max="6916" width="16.85546875" customWidth="1"/>
+    <col min="6917" max="6917" width="13.85546875" customWidth="1"/>
+    <col min="7169" max="7169" width="64.85546875" customWidth="1"/>
+    <col min="7170" max="7170" width="12.5703125" customWidth="1"/>
+    <col min="7171" max="7171" width="16.5703125" customWidth="1"/>
+    <col min="7172" max="7172" width="16.85546875" customWidth="1"/>
+    <col min="7173" max="7173" width="13.85546875" customWidth="1"/>
+    <col min="7425" max="7425" width="64.85546875" customWidth="1"/>
+    <col min="7426" max="7426" width="12.5703125" customWidth="1"/>
+    <col min="7427" max="7427" width="16.5703125" customWidth="1"/>
+    <col min="7428" max="7428" width="16.85546875" customWidth="1"/>
+    <col min="7429" max="7429" width="13.85546875" customWidth="1"/>
+    <col min="7681" max="7681" width="64.85546875" customWidth="1"/>
+    <col min="7682" max="7682" width="12.5703125" customWidth="1"/>
+    <col min="7683" max="7683" width="16.5703125" customWidth="1"/>
+    <col min="7684" max="7684" width="16.85546875" customWidth="1"/>
+    <col min="7685" max="7685" width="13.85546875" customWidth="1"/>
+    <col min="7937" max="7937" width="64.85546875" customWidth="1"/>
+    <col min="7938" max="7938" width="12.5703125" customWidth="1"/>
+    <col min="7939" max="7939" width="16.5703125" customWidth="1"/>
+    <col min="7940" max="7940" width="16.85546875" customWidth="1"/>
+    <col min="7941" max="7941" width="13.85546875" customWidth="1"/>
+    <col min="8193" max="8193" width="64.85546875" customWidth="1"/>
+    <col min="8194" max="8194" width="12.5703125" customWidth="1"/>
+    <col min="8195" max="8195" width="16.5703125" customWidth="1"/>
+    <col min="8196" max="8196" width="16.85546875" customWidth="1"/>
+    <col min="8197" max="8197" width="13.85546875" customWidth="1"/>
+    <col min="8449" max="8449" width="64.85546875" customWidth="1"/>
+    <col min="8450" max="8450" width="12.5703125" customWidth="1"/>
+    <col min="8451" max="8451" width="16.5703125" customWidth="1"/>
+    <col min="8452" max="8452" width="16.85546875" customWidth="1"/>
+    <col min="8453" max="8453" width="13.85546875" customWidth="1"/>
+    <col min="8705" max="8705" width="64.85546875" customWidth="1"/>
+    <col min="8706" max="8706" width="12.5703125" customWidth="1"/>
+    <col min="8707" max="8707" width="16.5703125" customWidth="1"/>
+    <col min="8708" max="8708" width="16.85546875" customWidth="1"/>
+    <col min="8709" max="8709" width="13.85546875" customWidth="1"/>
+    <col min="8961" max="8961" width="64.85546875" customWidth="1"/>
+    <col min="8962" max="8962" width="12.5703125" customWidth="1"/>
+    <col min="8963" max="8963" width="16.5703125" customWidth="1"/>
+    <col min="8964" max="8964" width="16.85546875" customWidth="1"/>
+    <col min="8965" max="8965" width="13.85546875" customWidth="1"/>
+    <col min="9217" max="9217" width="64.85546875" customWidth="1"/>
+    <col min="9218" max="9218" width="12.5703125" customWidth="1"/>
+    <col min="9219" max="9219" width="16.5703125" customWidth="1"/>
+    <col min="9220" max="9220" width="16.85546875" customWidth="1"/>
+    <col min="9221" max="9221" width="13.85546875" customWidth="1"/>
+    <col min="9473" max="9473" width="64.85546875" customWidth="1"/>
+    <col min="9474" max="9474" width="12.5703125" customWidth="1"/>
+    <col min="9475" max="9475" width="16.5703125" customWidth="1"/>
+    <col min="9476" max="9476" width="16.85546875" customWidth="1"/>
+    <col min="9477" max="9477" width="13.85546875" customWidth="1"/>
+    <col min="9729" max="9729" width="64.85546875" customWidth="1"/>
+    <col min="9730" max="9730" width="12.5703125" customWidth="1"/>
+    <col min="9731" max="9731" width="16.5703125" customWidth="1"/>
+    <col min="9732" max="9732" width="16.85546875" customWidth="1"/>
+    <col min="9733" max="9733" width="13.85546875" customWidth="1"/>
+    <col min="9985" max="9985" width="64.85546875" customWidth="1"/>
+    <col min="9986" max="9986" width="12.5703125" customWidth="1"/>
+    <col min="9987" max="9987" width="16.5703125" customWidth="1"/>
+    <col min="9988" max="9988" width="16.85546875" customWidth="1"/>
+    <col min="9989" max="9989" width="13.85546875" customWidth="1"/>
+    <col min="10241" max="10241" width="64.85546875" customWidth="1"/>
+    <col min="10242" max="10242" width="12.5703125" customWidth="1"/>
+    <col min="10243" max="10243" width="16.5703125" customWidth="1"/>
+    <col min="10244" max="10244" width="16.85546875" customWidth="1"/>
+    <col min="10245" max="10245" width="13.85546875" customWidth="1"/>
+    <col min="10497" max="10497" width="64.85546875" customWidth="1"/>
+    <col min="10498" max="10498" width="12.5703125" customWidth="1"/>
+    <col min="10499" max="10499" width="16.5703125" customWidth="1"/>
+    <col min="10500" max="10500" width="16.85546875" customWidth="1"/>
+    <col min="10501" max="10501" width="13.85546875" customWidth="1"/>
+    <col min="10753" max="10753" width="64.85546875" customWidth="1"/>
+    <col min="10754" max="10754" width="12.5703125" customWidth="1"/>
+    <col min="10755" max="10755" width="16.5703125" customWidth="1"/>
+    <col min="10756" max="10756" width="16.85546875" customWidth="1"/>
+    <col min="10757" max="10757" width="13.85546875" customWidth="1"/>
+    <col min="11009" max="11009" width="64.85546875" customWidth="1"/>
+    <col min="11010" max="11010" width="12.5703125" customWidth="1"/>
+    <col min="11011" max="11011" width="16.5703125" customWidth="1"/>
+    <col min="11012" max="11012" width="16.85546875" customWidth="1"/>
+    <col min="11013" max="11013" width="13.85546875" customWidth="1"/>
+    <col min="11265" max="11265" width="64.85546875" customWidth="1"/>
+    <col min="11266" max="11266" width="12.5703125" customWidth="1"/>
+    <col min="11267" max="11267" width="16.5703125" customWidth="1"/>
+    <col min="11268" max="11268" width="16.85546875" customWidth="1"/>
+    <col min="11269" max="11269" width="13.85546875" customWidth="1"/>
+    <col min="11521" max="11521" width="64.85546875" customWidth="1"/>
+    <col min="11522" max="11522" width="12.5703125" customWidth="1"/>
+    <col min="11523" max="11523" width="16.5703125" customWidth="1"/>
+    <col min="11524" max="11524" width="16.85546875" customWidth="1"/>
+    <col min="11525" max="11525" width="13.85546875" customWidth="1"/>
+    <col min="11777" max="11777" width="64.85546875" customWidth="1"/>
+    <col min="11778" max="11778" width="12.5703125" customWidth="1"/>
+    <col min="11779" max="11779" width="16.5703125" customWidth="1"/>
+    <col min="11780" max="11780" width="16.85546875" customWidth="1"/>
+    <col min="11781" max="11781" width="13.85546875" customWidth="1"/>
+    <col min="12033" max="12033" width="64.85546875" customWidth="1"/>
+    <col min="12034" max="12034" width="12.5703125" customWidth="1"/>
+    <col min="12035" max="12035" width="16.5703125" customWidth="1"/>
+    <col min="12036" max="12036" width="16.85546875" customWidth="1"/>
+    <col min="12037" max="12037" width="13.85546875" customWidth="1"/>
+    <col min="12289" max="12289" width="64.85546875" customWidth="1"/>
+    <col min="12290" max="12290" width="12.5703125" customWidth="1"/>
+    <col min="12291" max="12291" width="16.5703125" customWidth="1"/>
+    <col min="12292" max="12292" width="16.85546875" customWidth="1"/>
+    <col min="12293" max="12293" width="13.85546875" customWidth="1"/>
+    <col min="12545" max="12545" width="64.85546875" customWidth="1"/>
+    <col min="12546" max="12546" width="12.5703125" customWidth="1"/>
+    <col min="12547" max="12547" width="16.5703125" customWidth="1"/>
+    <col min="12548" max="12548" width="16.85546875" customWidth="1"/>
+    <col min="12549" max="12549" width="13.85546875" customWidth="1"/>
+    <col min="12801" max="12801" width="64.85546875" customWidth="1"/>
+    <col min="12802" max="12802" width="12.5703125" customWidth="1"/>
+    <col min="12803" max="12803" width="16.5703125" customWidth="1"/>
+    <col min="12804" max="12804" width="16.85546875" customWidth="1"/>
+    <col min="12805" max="12805" width="13.85546875" customWidth="1"/>
+    <col min="13057" max="13057" width="64.85546875" customWidth="1"/>
+    <col min="13058" max="13058" width="12.5703125" customWidth="1"/>
+    <col min="13059" max="13059" width="16.5703125" customWidth="1"/>
+    <col min="13060" max="13060" width="16.85546875" customWidth="1"/>
+    <col min="13061" max="13061" width="13.85546875" customWidth="1"/>
+    <col min="13313" max="13313" width="64.85546875" customWidth="1"/>
+    <col min="13314" max="13314" width="12.5703125" customWidth="1"/>
+    <col min="13315" max="13315" width="16.5703125" customWidth="1"/>
+    <col min="13316" max="13316" width="16.85546875" customWidth="1"/>
+    <col min="13317" max="13317" width="13.85546875" customWidth="1"/>
+    <col min="13569" max="13569" width="64.85546875" customWidth="1"/>
+    <col min="13570" max="13570" width="12.5703125" customWidth="1"/>
+    <col min="13571" max="13571" width="16.5703125" customWidth="1"/>
+    <col min="13572" max="13572" width="16.85546875" customWidth="1"/>
+    <col min="13573" max="13573" width="13.85546875" customWidth="1"/>
+    <col min="13825" max="13825" width="64.85546875" customWidth="1"/>
+    <col min="13826" max="13826" width="12.5703125" customWidth="1"/>
+    <col min="13827" max="13827" width="16.5703125" customWidth="1"/>
+    <col min="13828" max="13828" width="16.85546875" customWidth="1"/>
+    <col min="13829" max="13829" width="13.85546875" customWidth="1"/>
+    <col min="14081" max="14081" width="64.85546875" customWidth="1"/>
+    <col min="14082" max="14082" width="12.5703125" customWidth="1"/>
+    <col min="14083" max="14083" width="16.5703125" customWidth="1"/>
+    <col min="14084" max="14084" width="16.85546875" customWidth="1"/>
+    <col min="14085" max="14085" width="13.85546875" customWidth="1"/>
+    <col min="14337" max="14337" width="64.85546875" customWidth="1"/>
+    <col min="14338" max="14338" width="12.5703125" customWidth="1"/>
+    <col min="14339" max="14339" width="16.5703125" customWidth="1"/>
+    <col min="14340" max="14340" width="16.85546875" customWidth="1"/>
+    <col min="14341" max="14341" width="13.85546875" customWidth="1"/>
+    <col min="14593" max="14593" width="64.85546875" customWidth="1"/>
+    <col min="14594" max="14594" width="12.5703125" customWidth="1"/>
+    <col min="14595" max="14595" width="16.5703125" customWidth="1"/>
+    <col min="14596" max="14596" width="16.85546875" customWidth="1"/>
+    <col min="14597" max="14597" width="13.85546875" customWidth="1"/>
+    <col min="14849" max="14849" width="64.85546875" customWidth="1"/>
+    <col min="14850" max="14850" width="12.5703125" customWidth="1"/>
+    <col min="14851" max="14851" width="16.5703125" customWidth="1"/>
+    <col min="14852" max="14852" width="16.85546875" customWidth="1"/>
+    <col min="14853" max="14853" width="13.85546875" customWidth="1"/>
+    <col min="15105" max="15105" width="64.85546875" customWidth="1"/>
+    <col min="15106" max="15106" width="12.5703125" customWidth="1"/>
+    <col min="15107" max="15107" width="16.5703125" customWidth="1"/>
+    <col min="15108" max="15108" width="16.85546875" customWidth="1"/>
+    <col min="15109" max="15109" width="13.85546875" customWidth="1"/>
+    <col min="15361" max="15361" width="64.85546875" customWidth="1"/>
+    <col min="15362" max="15362" width="12.5703125" customWidth="1"/>
+    <col min="15363" max="15363" width="16.5703125" customWidth="1"/>
+    <col min="15364" max="15364" width="16.85546875" customWidth="1"/>
+    <col min="15365" max="15365" width="13.85546875" customWidth="1"/>
+    <col min="15617" max="15617" width="64.85546875" customWidth="1"/>
+    <col min="15618" max="15618" width="12.5703125" customWidth="1"/>
+    <col min="15619" max="15619" width="16.5703125" customWidth="1"/>
+    <col min="15620" max="15620" width="16.85546875" customWidth="1"/>
+    <col min="15621" max="15621" width="13.85546875" customWidth="1"/>
+    <col min="15873" max="15873" width="64.85546875" customWidth="1"/>
+    <col min="15874" max="15874" width="12.5703125" customWidth="1"/>
+    <col min="15875" max="15875" width="16.5703125" customWidth="1"/>
+    <col min="15876" max="15876" width="16.85546875" customWidth="1"/>
+    <col min="15877" max="15877" width="13.85546875" customWidth="1"/>
+    <col min="16129" max="16129" width="64.85546875" customWidth="1"/>
+    <col min="16130" max="16130" width="12.5703125" customWidth="1"/>
+    <col min="16131" max="16131" width="16.5703125" customWidth="1"/>
+    <col min="16132" max="16132" width="16.85546875" customWidth="1"/>
+    <col min="16133" max="16133" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="265" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="266" t="s">
+        <v>831</v>
+      </c>
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="265" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" s="265"/>
+      <c r="C3" s="265"/>
+      <c r="D3" s="265"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="262"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="266" t="s">
+        <v>832</v>
+      </c>
+      <c r="B5" s="266"/>
+      <c r="C5" s="266"/>
+      <c r="D5" s="266"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="265"/>
+      <c r="B6" s="265"/>
+      <c r="C6" s="265"/>
+      <c r="D6" s="265"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="269" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="269"/>
+      <c r="C7" s="269"/>
+      <c r="D7" s="269"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="270" t="s">
+        <v>833</v>
+      </c>
+      <c r="B8" s="270" t="s">
+        <v>834</v>
+      </c>
+      <c r="C8" s="270" t="s">
+        <v>835</v>
+      </c>
+      <c r="D8" s="270" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="271"/>
+      <c r="B9" s="271"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="271"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="272"/>
+      <c r="B10" s="272"/>
+      <c r="C10" s="272"/>
+      <c r="D10" s="272"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="180" t="s">
+        <v>347</v>
+      </c>
+      <c r="B11" s="181">
+        <v>10101010</v>
+      </c>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="183"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="184" t="s">
+        <v>837</v>
+      </c>
+      <c r="B12" s="185">
+        <v>10101020</v>
+      </c>
+      <c r="C12" s="182"/>
+      <c r="D12" s="182"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="184" t="s">
+        <v>838</v>
+      </c>
+      <c r="B13" s="185">
+        <v>10102020</v>
+      </c>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="186"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="184" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="185">
+        <v>10205990</v>
+      </c>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="184" t="s">
+        <v>388</v>
+      </c>
+      <c r="B15" s="185">
+        <v>10301020</v>
+      </c>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="184" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="185">
+        <v>10303010</v>
+      </c>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="184" t="s">
+        <v>839</v>
+      </c>
+      <c r="B17" s="185">
+        <v>10303020</v>
+      </c>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="184" t="s">
+        <v>840</v>
+      </c>
+      <c r="B18" s="185">
+        <v>10303030</v>
+      </c>
+      <c r="C18" s="182"/>
+      <c r="D18" s="182"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="184" t="s">
+        <v>419</v>
+      </c>
+      <c r="B19" s="185">
+        <v>10304050</v>
+      </c>
+      <c r="C19" s="182"/>
+      <c r="D19" s="182"/>
+      <c r="E19" s="183">
+        <f>C19-D19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="184" t="s">
+        <v>423</v>
+      </c>
+      <c r="B20" s="185">
+        <v>10305010</v>
+      </c>
+      <c r="C20" s="182"/>
+      <c r="D20" s="182"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="184" t="s">
+        <v>424</v>
+      </c>
+      <c r="B21" s="185">
+        <v>10305020</v>
+      </c>
+      <c r="C21" s="182"/>
+      <c r="D21" s="182"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="184" t="s">
+        <v>841</v>
+      </c>
+      <c r="B22" s="185">
+        <v>10305040</v>
+      </c>
+      <c r="C22" s="182"/>
+      <c r="D22" s="182"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="184" t="s">
+        <v>842</v>
+      </c>
+      <c r="B23" s="185">
+        <v>10306010</v>
+      </c>
+      <c r="C23" s="182"/>
+      <c r="D23" s="182"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="184" t="s">
+        <v>430</v>
+      </c>
+      <c r="B24" s="185">
+        <v>10306020</v>
+      </c>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="184" t="s">
+        <v>434</v>
+      </c>
+      <c r="B25" s="185">
+        <v>10306990</v>
+      </c>
+      <c r="C25" s="182"/>
+      <c r="D25" s="182"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="184" t="s">
+        <v>843</v>
+      </c>
+      <c r="B26" s="185">
+        <v>10402090</v>
+      </c>
+      <c r="C26" s="182"/>
+      <c r="D26" s="182"/>
+    </row>
+    <row r="27" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="184" t="s">
+        <v>456</v>
+      </c>
+      <c r="B27" s="185">
+        <v>10404010</v>
+      </c>
+      <c r="C27" s="182"/>
+      <c r="D27" s="182"/>
+      <c r="E27" s="183">
+        <f>C27-D27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="184" t="s">
+        <v>844</v>
+      </c>
+      <c r="B28" s="185">
+        <v>10404060</v>
+      </c>
+      <c r="C28" s="182"/>
+      <c r="D28" s="182"/>
+      <c r="E28" s="183">
+        <f t="shared" ref="E28:E80" si="0">C28-D28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="184" t="s">
+        <v>845</v>
+      </c>
+      <c r="B29" s="185">
+        <v>10404070</v>
+      </c>
+      <c r="C29" s="182"/>
+      <c r="D29" s="182"/>
+      <c r="E29" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="184" t="s">
+        <v>846</v>
+      </c>
+      <c r="B30" s="185">
+        <v>10404090</v>
+      </c>
+      <c r="C30" s="182"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="184" t="s">
+        <v>847</v>
+      </c>
+      <c r="B31" s="185">
+        <v>10404990</v>
+      </c>
+      <c r="C31" s="182"/>
+      <c r="D31" s="182"/>
+      <c r="E31" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="184" t="s">
+        <v>473</v>
+      </c>
+      <c r="B32" s="185">
+        <v>10501010</v>
+      </c>
+      <c r="C32" s="182"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="184" t="s">
+        <v>477</v>
+      </c>
+      <c r="B33" s="185">
+        <v>10501050</v>
+      </c>
+      <c r="C33" s="182"/>
+      <c r="D33" s="182"/>
+      <c r="E33" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="184" t="s">
+        <v>478</v>
+      </c>
+      <c r="B34" s="185">
+        <v>10501990</v>
+      </c>
+      <c r="C34" s="182"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="184" t="s">
+        <v>848</v>
+      </c>
+      <c r="B35" s="185">
+        <v>10601030</v>
+      </c>
+      <c r="C35" s="182"/>
+      <c r="D35" s="182"/>
+      <c r="E35" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="184" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" s="185">
+        <v>10701010</v>
+      </c>
+      <c r="C36" s="182"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="184" t="s">
+        <v>849</v>
+      </c>
+      <c r="B37" s="185">
+        <v>10702010</v>
+      </c>
+      <c r="C37" s="182"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="184" t="s">
+        <v>505</v>
+      </c>
+      <c r="B38" s="185">
+        <v>10703010</v>
+      </c>
+      <c r="C38" s="182"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="184" t="s">
+        <v>850</v>
+      </c>
+      <c r="B39" s="185">
+        <v>10703020</v>
+      </c>
+      <c r="C39" s="182"/>
+      <c r="D39" s="182"/>
+      <c r="E39" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="184" t="s">
+        <v>851</v>
+      </c>
+      <c r="B40" s="185">
+        <v>10703040</v>
+      </c>
+      <c r="C40" s="182"/>
+      <c r="D40" s="182"/>
+      <c r="E40" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="184" t="s">
+        <v>517</v>
+      </c>
+      <c r="B41" s="185">
+        <v>10703050</v>
+      </c>
+      <c r="C41" s="182"/>
+      <c r="D41" s="182"/>
+      <c r="E41" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="184" t="s">
+        <v>852</v>
+      </c>
+      <c r="B42" s="185">
+        <v>10703051</v>
+      </c>
+      <c r="C42" s="182"/>
+      <c r="D42" s="182"/>
+      <c r="E42" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="184" t="s">
+        <v>536</v>
+      </c>
+      <c r="B43" s="185">
+        <v>10704010</v>
+      </c>
+      <c r="C43" s="182"/>
+      <c r="D43" s="182"/>
+      <c r="E43" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="184" t="s">
+        <v>853</v>
+      </c>
+      <c r="B44" s="185">
+        <v>10704020</v>
+      </c>
+      <c r="C44" s="182"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="184" t="s">
+        <v>854</v>
+      </c>
+      <c r="B45" s="185">
+        <v>10704040</v>
+      </c>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="184" t="s">
+        <v>855</v>
+      </c>
+      <c r="B46" s="185">
+        <v>10704050</v>
+      </c>
+      <c r="C46" s="182"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="184" t="s">
+        <v>856</v>
+      </c>
+      <c r="B47" s="185">
+        <v>10704990</v>
+      </c>
+      <c r="C47" s="182"/>
+      <c r="D47" s="182"/>
+      <c r="E47" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="184" t="s">
+        <v>558</v>
+      </c>
+      <c r="B48" s="185">
+        <v>10705010</v>
+      </c>
+      <c r="C48" s="182"/>
+      <c r="D48" s="182"/>
+      <c r="E48" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="184" t="s">
+        <v>857</v>
+      </c>
+      <c r="B49" s="185">
+        <v>10705011</v>
+      </c>
+      <c r="C49" s="182"/>
+      <c r="D49" s="182"/>
+      <c r="E49" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="184" t="s">
+        <v>561</v>
+      </c>
+      <c r="B50" s="185">
+        <v>10705020</v>
+      </c>
+      <c r="C50" s="182"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="184" t="s">
+        <v>858</v>
+      </c>
+      <c r="B51" s="185">
+        <v>10705021</v>
+      </c>
+      <c r="C51" s="182"/>
+      <c r="D51" s="182"/>
+      <c r="E51" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="184" t="s">
+        <v>859</v>
+      </c>
+      <c r="B52" s="185">
+        <v>10705030</v>
+      </c>
+      <c r="C52" s="182"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="187" t="s">
+        <v>860</v>
+      </c>
+      <c r="B53" s="185">
+        <v>10705031</v>
+      </c>
+      <c r="C53" s="182"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="184" t="s">
+        <v>861</v>
+      </c>
+      <c r="B54" s="185">
+        <v>10705040</v>
+      </c>
+      <c r="C54" s="182"/>
+      <c r="D54" s="182"/>
+      <c r="E54" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="188" t="s">
+        <v>862</v>
+      </c>
+      <c r="B55" s="185">
+        <v>10705041</v>
+      </c>
+      <c r="C55" s="182"/>
+      <c r="D55" s="182"/>
+      <c r="E55" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="184" t="s">
+        <v>576</v>
+      </c>
+      <c r="B56" s="185">
+        <v>10705070</v>
+      </c>
+      <c r="C56" s="182"/>
+      <c r="D56" s="182"/>
+      <c r="E56" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="184" t="s">
+        <v>863</v>
+      </c>
+      <c r="B57" s="185">
+        <v>10705071</v>
+      </c>
+      <c r="C57" s="182"/>
+      <c r="D57" s="182"/>
+      <c r="E57" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="184" t="s">
+        <v>864</v>
+      </c>
+      <c r="B58" s="185">
+        <v>10705080</v>
+      </c>
+      <c r="C58" s="182"/>
+      <c r="D58" s="182"/>
+      <c r="E58" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="188" t="s">
+        <v>865</v>
+      </c>
+      <c r="B59" s="185">
+        <v>10705081</v>
+      </c>
+      <c r="C59" s="182"/>
+      <c r="D59" s="182"/>
+      <c r="E59" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="188" t="s">
+        <v>866</v>
+      </c>
+      <c r="B60" s="185">
+        <v>10705090</v>
+      </c>
+      <c r="C60" s="182"/>
+      <c r="D60" s="182"/>
+      <c r="E60" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="190" t="s">
+        <v>867</v>
+      </c>
+      <c r="B61" s="185">
+        <v>10705091</v>
+      </c>
+      <c r="C61" s="182"/>
+      <c r="D61" s="182"/>
+      <c r="E61" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="184" t="s">
+        <v>868</v>
+      </c>
+      <c r="B62" s="185">
+        <v>10705100</v>
+      </c>
+      <c r="C62" s="182"/>
+      <c r="D62" s="182"/>
+      <c r="E62" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="190" t="s">
+        <v>869</v>
+      </c>
+      <c r="B63" s="185">
+        <v>10705101</v>
+      </c>
+      <c r="C63" s="182"/>
+      <c r="D63" s="182"/>
+      <c r="E63" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="184" t="s">
+        <v>588</v>
+      </c>
+      <c r="B64" s="185">
+        <v>10705110</v>
+      </c>
+      <c r="C64" s="182"/>
+      <c r="D64" s="182"/>
+      <c r="E64" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="188" t="s">
+        <v>870</v>
+      </c>
+      <c r="B65" s="185">
+        <v>10705111</v>
+      </c>
+      <c r="C65" s="182"/>
+      <c r="D65" s="182"/>
+      <c r="E65" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="184" t="s">
+        <v>594</v>
+      </c>
+      <c r="B66" s="185">
+        <v>10705130</v>
+      </c>
+      <c r="C66" s="182"/>
+      <c r="D66" s="182"/>
+      <c r="E66" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="184" t="s">
+        <v>871</v>
+      </c>
+      <c r="B67" s="185">
+        <v>10705140</v>
+      </c>
+      <c r="C67" s="182"/>
+      <c r="D67" s="182"/>
+      <c r="E67" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="184" t="s">
+        <v>872</v>
+      </c>
+      <c r="B68" s="185">
+        <v>10705990</v>
+      </c>
+      <c r="C68" s="182"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="188" t="s">
+        <v>873</v>
+      </c>
+      <c r="B69" s="185">
+        <v>10705991</v>
+      </c>
+      <c r="C69" s="182"/>
+      <c r="D69" s="182"/>
+      <c r="E69" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="184" t="s">
+        <v>604</v>
+      </c>
+      <c r="B70" s="185">
+        <v>10706010</v>
+      </c>
+      <c r="C70" s="182"/>
+      <c r="D70" s="182"/>
+      <c r="E70" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="184" t="s">
+        <v>874</v>
+      </c>
+      <c r="B71" s="185">
+        <v>10706011</v>
+      </c>
+      <c r="C71" s="182"/>
+      <c r="D71" s="182"/>
+      <c r="E71" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="184" t="s">
+        <v>875</v>
+      </c>
+      <c r="B72" s="185">
+        <v>10707010</v>
+      </c>
+      <c r="C72" s="182"/>
+      <c r="D72" s="182"/>
+      <c r="E72" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="184" t="s">
+        <v>876</v>
+      </c>
+      <c r="B73" s="185">
+        <v>10707011</v>
+      </c>
+      <c r="C73" s="182"/>
+      <c r="D73" s="182"/>
+      <c r="E73" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="184" t="s">
+        <v>877</v>
+      </c>
+      <c r="B74" s="185">
+        <v>10707020</v>
+      </c>
+      <c r="C74" s="182"/>
+      <c r="D74" s="182"/>
+      <c r="E74" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="184" t="s">
+        <v>878</v>
+      </c>
+      <c r="B75" s="185">
+        <v>10710010</v>
+      </c>
+      <c r="C75" s="182"/>
+      <c r="D75" s="182"/>
+      <c r="E75" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="184" t="s">
+        <v>879</v>
+      </c>
+      <c r="B76" s="185">
+        <v>10710020</v>
+      </c>
+      <c r="C76" s="182"/>
+      <c r="D76" s="182"/>
+      <c r="E76" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="184" t="s">
+        <v>880</v>
+      </c>
+      <c r="B77" s="185">
+        <v>10710030</v>
+      </c>
+      <c r="C77" s="182"/>
+      <c r="D77" s="182"/>
+      <c r="E77" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="188" t="s">
+        <v>881</v>
+      </c>
+      <c r="B78" s="185">
+        <v>10707021</v>
+      </c>
+      <c r="C78" s="182"/>
+      <c r="D78" s="182"/>
+      <c r="E78" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="184" t="s">
+        <v>882</v>
+      </c>
+      <c r="B79" s="185">
+        <v>10799990</v>
+      </c>
+      <c r="C79" s="182"/>
+      <c r="D79" s="182"/>
+      <c r="E79" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="188" t="s">
+        <v>883</v>
+      </c>
+      <c r="B80" s="185">
+        <v>10799991</v>
+      </c>
+      <c r="C80" s="182"/>
+      <c r="D80" s="182"/>
+      <c r="E80" s="183">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="184" t="s">
+        <v>679</v>
+      </c>
+      <c r="B81" s="185">
+        <v>10901020</v>
+      </c>
+      <c r="C81" s="182"/>
+      <c r="D81" s="182"/>
+    </row>
+    <row r="82" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="184" t="s">
+        <v>682</v>
+      </c>
+      <c r="B82" s="185">
+        <v>10901990</v>
+      </c>
+      <c r="C82" s="182"/>
+      <c r="D82" s="182"/>
+    </row>
+    <row r="83" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="184" t="s">
+        <v>884</v>
+      </c>
+      <c r="B83" s="185">
+        <v>20101020</v>
+      </c>
+      <c r="C83" s="182"/>
+      <c r="D83" s="182"/>
+    </row>
+    <row r="84" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="184" t="s">
+        <v>885</v>
+      </c>
+      <c r="B84" s="185">
+        <v>20102040</v>
+      </c>
+      <c r="C84" s="182"/>
+      <c r="D84" s="182"/>
+    </row>
+    <row r="85" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="184" t="s">
+        <v>714</v>
+      </c>
+      <c r="B85" s="185">
+        <v>20201010</v>
+      </c>
+      <c r="C85" s="182"/>
+      <c r="D85" s="182"/>
+      <c r="E85" s="183">
+        <f>C85-D85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="184" t="s">
+        <v>715</v>
+      </c>
+      <c r="B86" s="185">
+        <v>20201020</v>
+      </c>
+      <c r="C86" s="182"/>
+      <c r="D86" s="182"/>
+    </row>
+    <row r="87" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="184" t="s">
+        <v>886</v>
+      </c>
+      <c r="B87" s="185">
+        <v>20201030</v>
+      </c>
+      <c r="C87" s="182"/>
+      <c r="D87" s="182"/>
+    </row>
+    <row r="88" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="184" t="s">
+        <v>887</v>
+      </c>
+      <c r="B88" s="185">
+        <v>20201040</v>
+      </c>
+      <c r="C88" s="182"/>
+      <c r="D88" s="182"/>
+    </row>
+    <row r="89" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="184" t="s">
+        <v>718</v>
+      </c>
+      <c r="B89" s="185">
+        <v>20201050</v>
+      </c>
+      <c r="C89" s="182"/>
+      <c r="D89" s="182"/>
+    </row>
+    <row r="90" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="184" t="s">
+        <v>719</v>
+      </c>
+      <c r="B90" s="185">
+        <v>20201060</v>
+      </c>
+      <c r="C90" s="182"/>
+      <c r="D90" s="182"/>
+    </row>
+    <row r="91" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="184" t="s">
+        <v>720</v>
+      </c>
+      <c r="B91" s="185">
+        <v>20201070</v>
+      </c>
+      <c r="C91" s="182"/>
+      <c r="D91" s="182"/>
+    </row>
+    <row r="92" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="184" t="s">
+        <v>724</v>
+      </c>
+      <c r="B92" s="185">
+        <v>20301010</v>
+      </c>
+      <c r="C92" s="182"/>
+      <c r="D92" s="182"/>
+    </row>
+    <row r="93" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="184" t="s">
+        <v>888</v>
+      </c>
+      <c r="B93" s="185">
+        <v>20401040</v>
+      </c>
+      <c r="C93" s="182"/>
+      <c r="D93" s="182"/>
+    </row>
+    <row r="94" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="184" t="s">
+        <v>889</v>
+      </c>
+      <c r="B94" s="185">
+        <v>20501010</v>
+      </c>
+      <c r="C94" s="182"/>
+      <c r="D94" s="182"/>
+    </row>
+    <row r="95" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="184" t="s">
+        <v>746</v>
+      </c>
+      <c r="B95" s="185">
+        <v>29999990</v>
+      </c>
+      <c r="C95" s="182"/>
+      <c r="D95" s="182"/>
+    </row>
+    <row r="96" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="184" t="s">
+        <v>776</v>
+      </c>
+      <c r="B96" s="185">
+        <v>30101010</v>
+      </c>
+      <c r="C96" s="182"/>
+      <c r="D96" s="182"/>
+    </row>
+    <row r="97" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="184" t="s">
+        <v>890</v>
+      </c>
+      <c r="B97" s="185">
+        <v>30101020</v>
+      </c>
+      <c r="C97" s="182"/>
+      <c r="D97" s="182"/>
+    </row>
+    <row r="98" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="184" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" s="185">
+        <v>40101020</v>
+      </c>
+      <c r="C98" s="182"/>
+      <c r="D98" s="182"/>
+    </row>
+    <row r="99" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="184" t="s">
+        <v>891</v>
+      </c>
+      <c r="B99" s="185">
+        <v>40101050</v>
+      </c>
+      <c r="C99" s="182"/>
+      <c r="D99" s="182"/>
+    </row>
+    <row r="100" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="184" t="s">
+        <v>892</v>
+      </c>
+      <c r="B100" s="185">
+        <v>40102040</v>
+      </c>
+      <c r="C100" s="182"/>
+      <c r="D100" s="182"/>
+    </row>
+    <row r="101" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="184" t="s">
+        <v>37</v>
+      </c>
+      <c r="B101" s="185">
+        <v>40102041</v>
+      </c>
+      <c r="C101" s="182"/>
+      <c r="D101" s="182"/>
+    </row>
+    <row r="102" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="184" t="s">
+        <v>42</v>
+      </c>
+      <c r="B102" s="185">
+        <v>40102080</v>
+      </c>
+      <c r="C102" s="182"/>
+      <c r="D102" s="182"/>
+    </row>
+    <row r="103" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="184" t="s">
+        <v>893</v>
+      </c>
+      <c r="B103" s="185">
+        <v>40103030</v>
+      </c>
+      <c r="C103" s="182"/>
+      <c r="D103" s="182"/>
+    </row>
+    <row r="104" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="184" t="s">
+        <v>894</v>
+      </c>
+      <c r="B104" s="185">
+        <v>40103040</v>
+      </c>
+      <c r="C104" s="182"/>
+      <c r="D104" s="182"/>
+    </row>
+    <row r="105" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="184" t="s">
+        <v>895</v>
+      </c>
+      <c r="B105" s="185">
+        <v>40103050</v>
+      </c>
+      <c r="C105" s="182"/>
+      <c r="D105" s="182"/>
+    </row>
+    <row r="106" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="184" t="s">
+        <v>896</v>
+      </c>
+      <c r="B106" s="185">
+        <v>40103060</v>
+      </c>
+      <c r="C106" s="182"/>
+      <c r="D106" s="182"/>
+    </row>
+    <row r="107" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="184" t="s">
+        <v>897</v>
+      </c>
+      <c r="B107" s="185">
+        <v>40103070</v>
+      </c>
+      <c r="C107" s="182"/>
+      <c r="D107" s="182"/>
+    </row>
+    <row r="108" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="184" t="s">
+        <v>51</v>
+      </c>
+      <c r="B108" s="185">
+        <v>40104990</v>
+      </c>
+      <c r="C108" s="182"/>
+      <c r="D108" s="182"/>
+    </row>
+    <row r="109" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="184" t="s">
+        <v>898</v>
+      </c>
+      <c r="B109" s="185">
+        <v>40105020</v>
+      </c>
+      <c r="C109" s="182"/>
+      <c r="D109" s="182"/>
+    </row>
+    <row r="110" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="184" t="s">
+        <v>59</v>
+      </c>
+      <c r="B110" s="185">
+        <v>40106010</v>
+      </c>
+      <c r="C110" s="182"/>
+      <c r="D110" s="182"/>
+    </row>
+    <row r="111" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="184" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" s="185">
+        <v>40106030</v>
+      </c>
+      <c r="C111" s="182"/>
+      <c r="D111" s="182"/>
+    </row>
+    <row r="112" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="184" t="s">
+        <v>68</v>
+      </c>
+      <c r="B112" s="185">
+        <v>40201010</v>
+      </c>
+      <c r="C112" s="182"/>
+      <c r="D112" s="182"/>
+    </row>
+    <row r="113" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="184" t="s">
+        <v>69</v>
+      </c>
+      <c r="B113" s="185">
+        <v>40201020</v>
+      </c>
+      <c r="C113" s="182"/>
+      <c r="D113" s="182"/>
+    </row>
+    <row r="114" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="184" t="s">
+        <v>899</v>
+      </c>
+      <c r="B114" s="185">
+        <v>40201030</v>
+      </c>
+      <c r="C114" s="182"/>
+      <c r="D114" s="182"/>
+    </row>
+    <row r="115" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="184" t="s">
+        <v>900</v>
+      </c>
+      <c r="B115" s="185">
+        <v>40201040</v>
+      </c>
+      <c r="C115" s="182"/>
+      <c r="D115" s="182"/>
+    </row>
+    <row r="116" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="184" t="s">
+        <v>73</v>
+      </c>
+      <c r="B116" s="185">
+        <v>40201100</v>
+      </c>
+      <c r="C116" s="182"/>
+      <c r="D116" s="182"/>
+    </row>
+    <row r="117" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="184" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" s="185">
+        <v>40201140</v>
+      </c>
+      <c r="C117" s="182"/>
+      <c r="D117" s="182"/>
+    </row>
+    <row r="118" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="184" t="s">
+        <v>901</v>
+      </c>
+      <c r="B118" s="185">
+        <v>40201160</v>
+      </c>
+      <c r="C118" s="182"/>
+      <c r="D118" s="182"/>
+    </row>
+    <row r="119" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="184" t="s">
+        <v>902</v>
+      </c>
+      <c r="B119" s="185">
+        <v>40201980</v>
+      </c>
+      <c r="C119" s="182"/>
+      <c r="D119" s="182"/>
+    </row>
+    <row r="120" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="184" t="s">
+        <v>80</v>
+      </c>
+      <c r="B120" s="185">
+        <v>40201990</v>
+      </c>
+      <c r="C120" s="182"/>
+      <c r="D120" s="182"/>
+    </row>
+    <row r="121" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="184" t="s">
+        <v>903</v>
+      </c>
+      <c r="B121" s="185">
+        <v>40202050</v>
+      </c>
+      <c r="C121" s="182"/>
+      <c r="D121" s="182"/>
+    </row>
+    <row r="122" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="184" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" s="185">
+        <v>40202140</v>
+      </c>
+      <c r="C122" s="182"/>
+      <c r="D122" s="182"/>
+    </row>
+    <row r="123" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="184" t="s">
+        <v>904</v>
+      </c>
+      <c r="B123" s="185">
+        <v>40202150</v>
+      </c>
+      <c r="C123" s="182"/>
+      <c r="D123" s="182"/>
+    </row>
+    <row r="124" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="184" t="s">
+        <v>96</v>
+      </c>
+      <c r="B124" s="185">
+        <v>40202160</v>
+      </c>
+      <c r="C124" s="182"/>
+      <c r="D124" s="182"/>
+    </row>
+    <row r="125" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="184" t="s">
+        <v>106</v>
+      </c>
+      <c r="B125" s="185">
+        <v>40202190</v>
+      </c>
+      <c r="C125" s="182"/>
+      <c r="D125" s="182"/>
+    </row>
+    <row r="126" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="184" t="s">
+        <v>785</v>
+      </c>
+      <c r="B126" s="185">
+        <v>40202220</v>
+      </c>
+      <c r="C126" s="182"/>
+      <c r="D126" s="182"/>
+    </row>
+    <row r="127" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="184" t="s">
+        <v>905</v>
+      </c>
+      <c r="B127" s="185">
+        <v>40202980</v>
+      </c>
+      <c r="C127" s="182"/>
+      <c r="D127" s="182"/>
+    </row>
+    <row r="128" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="184" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" s="185">
+        <v>40202990</v>
+      </c>
+      <c r="C128" s="182"/>
+      <c r="D128" s="182"/>
+    </row>
+    <row r="129" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="184" t="s">
+        <v>906</v>
+      </c>
+      <c r="B129" s="185">
+        <v>40301010</v>
+      </c>
+      <c r="C129" s="182"/>
+      <c r="D129" s="182"/>
+    </row>
+    <row r="130" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="184" t="s">
+        <v>907</v>
+      </c>
+      <c r="B130" s="185">
+        <v>40302010</v>
+      </c>
+      <c r="C130" s="182"/>
+      <c r="D130" s="182"/>
+    </row>
+    <row r="131" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="184" t="s">
+        <v>120</v>
+      </c>
+      <c r="B131" s="185">
+        <v>40401020</v>
+      </c>
+      <c r="C131" s="182"/>
+      <c r="D131" s="182"/>
+    </row>
+    <row r="132" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="184" t="s">
+        <v>908</v>
+      </c>
+      <c r="B132" s="185">
+        <v>40402010</v>
+      </c>
+      <c r="C132" s="182"/>
+      <c r="D132" s="182"/>
+    </row>
+    <row r="133" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="184" t="s">
+        <v>909</v>
+      </c>
+      <c r="B133" s="185">
+        <v>40402020</v>
+      </c>
+      <c r="C133" s="182"/>
+      <c r="D133" s="182"/>
+    </row>
+    <row r="134" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="184" t="s">
+        <v>327</v>
+      </c>
+      <c r="B134" s="185">
+        <v>40601010</v>
+      </c>
+      <c r="C134" s="182"/>
+      <c r="D134" s="182"/>
+    </row>
+    <row r="135" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="184" t="s">
+        <v>910</v>
+      </c>
+      <c r="B135" s="185">
+        <v>50101010</v>
+      </c>
+      <c r="C135" s="182"/>
+      <c r="D135" s="182"/>
+    </row>
+    <row r="136" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="184" t="s">
+        <v>911</v>
+      </c>
+      <c r="B136" s="185">
+        <v>50101020</v>
+      </c>
+      <c r="C136" s="182"/>
+      <c r="D136" s="182"/>
+    </row>
+    <row r="137" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="184" t="s">
+        <v>912</v>
+      </c>
+      <c r="B137" s="185">
+        <v>50102010</v>
+      </c>
+      <c r="C137" s="182"/>
+      <c r="D137" s="182"/>
+    </row>
+    <row r="138" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="184" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" s="185">
+        <v>50102020</v>
+      </c>
+      <c r="C138" s="182"/>
+      <c r="D138" s="182"/>
+    </row>
+    <row r="139" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="184" t="s">
+        <v>141</v>
+      </c>
+      <c r="B139" s="185">
+        <v>50102030</v>
+      </c>
+      <c r="C139" s="182"/>
+      <c r="D139" s="182"/>
+    </row>
+    <row r="140" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="B140" s="185">
+        <v>50102040</v>
+      </c>
+      <c r="C140" s="182"/>
+      <c r="D140" s="182"/>
+    </row>
+    <row r="141" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="184" t="s">
+        <v>143</v>
+      </c>
+      <c r="B141" s="185">
+        <v>50102050</v>
+      </c>
+      <c r="C141" s="182"/>
+      <c r="D141" s="182"/>
+    </row>
+    <row r="142" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="184" t="s">
+        <v>913</v>
+      </c>
+      <c r="B142" s="185">
+        <v>50102060</v>
+      </c>
+      <c r="C142" s="182"/>
+      <c r="D142" s="182"/>
+    </row>
+    <row r="143" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="184" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" s="185">
+        <v>50102100</v>
+      </c>
+      <c r="C143" s="182"/>
+      <c r="D143" s="182"/>
+    </row>
+    <row r="144" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="184" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" s="185">
+        <v>50102110</v>
+      </c>
+      <c r="C144" s="182"/>
+      <c r="D144" s="182"/>
+    </row>
+    <row r="145" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="184" t="s">
+        <v>914</v>
+      </c>
+      <c r="B145" s="185">
+        <v>50102130</v>
+      </c>
+      <c r="C145" s="182"/>
+      <c r="D145" s="182"/>
+    </row>
+    <row r="146" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="184" t="s">
+        <v>915</v>
+      </c>
+      <c r="B146" s="185">
+        <v>50102140</v>
+      </c>
+      <c r="C146" s="182"/>
+      <c r="D146" s="182"/>
+    </row>
+    <row r="147" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="184" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" s="185">
+        <v>50102150</v>
+      </c>
+      <c r="C147" s="182"/>
+      <c r="D147" s="182"/>
+    </row>
+    <row r="148" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="184" t="s">
+        <v>916</v>
+      </c>
+      <c r="B148" s="185">
+        <v>50102990</v>
+      </c>
+      <c r="C148" s="182"/>
+      <c r="D148" s="182"/>
+    </row>
+    <row r="149" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="184" t="s">
+        <v>917</v>
+      </c>
+      <c r="B149" s="185">
+        <v>50103010</v>
+      </c>
+      <c r="C149" s="182"/>
+      <c r="D149" s="182"/>
+    </row>
+    <row r="150" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="184" t="s">
+        <v>918</v>
+      </c>
+      <c r="B150" s="185">
+        <v>50103020</v>
+      </c>
+      <c r="C150" s="182"/>
+      <c r="D150" s="182"/>
+    </row>
+    <row r="151" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="184" t="s">
+        <v>919</v>
+      </c>
+      <c r="B151" s="185">
+        <v>50103030</v>
+      </c>
+      <c r="C151" s="182"/>
+      <c r="D151" s="182"/>
+    </row>
+    <row r="152" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="184" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="185">
+        <v>50103040</v>
+      </c>
+      <c r="C152" s="182"/>
+      <c r="D152" s="182"/>
+    </row>
+    <row r="153" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="184" t="s">
+        <v>164</v>
+      </c>
+      <c r="B153" s="185">
+        <v>50104030</v>
+      </c>
+      <c r="C153" s="182"/>
+      <c r="D153" s="182"/>
+    </row>
+    <row r="154" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="184" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="185">
+        <v>50104990</v>
+      </c>
+      <c r="C154" s="182"/>
+      <c r="D154" s="182"/>
+    </row>
+    <row r="155" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="184" t="s">
+        <v>920</v>
+      </c>
+      <c r="B155" s="185">
+        <v>50201010</v>
+      </c>
+      <c r="C155" s="182"/>
+      <c r="D155" s="182"/>
+    </row>
+    <row r="156" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="184" t="s">
+        <v>171</v>
+      </c>
+      <c r="B156" s="185">
+        <v>50202010</v>
+      </c>
+      <c r="C156" s="182"/>
+      <c r="D156" s="182"/>
+    </row>
+    <row r="157" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="184" t="s">
+        <v>921</v>
+      </c>
+      <c r="B157" s="185">
+        <v>50203010</v>
+      </c>
+      <c r="C157" s="182"/>
+      <c r="D157" s="182"/>
+    </row>
+    <row r="158" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="184" t="s">
+        <v>175</v>
+      </c>
+      <c r="B158" s="185">
+        <v>50203020</v>
+      </c>
+      <c r="C158" s="182"/>
+      <c r="D158" s="182"/>
+    </row>
+    <row r="159" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="184" t="s">
+        <v>922</v>
+      </c>
+      <c r="B159" s="185">
+        <v>50203030</v>
+      </c>
+      <c r="C159" s="182"/>
+      <c r="D159" s="182"/>
+    </row>
+    <row r="160" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="184" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160" s="185">
+        <v>50203040</v>
+      </c>
+      <c r="C160" s="182"/>
+      <c r="D160" s="182"/>
+    </row>
+    <row r="161" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="184" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161" s="185">
+        <v>50203050</v>
+      </c>
+      <c r="C161" s="182"/>
+      <c r="D161" s="182"/>
+    </row>
+    <row r="162" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="184" t="s">
+        <v>179</v>
+      </c>
+      <c r="B162" s="185">
+        <v>50203060</v>
+      </c>
+      <c r="C162" s="182"/>
+      <c r="D162" s="182"/>
+    </row>
+    <row r="163" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="184" t="s">
+        <v>923</v>
+      </c>
+      <c r="B163" s="185">
+        <v>50203070</v>
+      </c>
+      <c r="C163" s="182"/>
+      <c r="D163" s="182"/>
+    </row>
+    <row r="164" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="184" t="s">
+        <v>924</v>
+      </c>
+      <c r="B164" s="185">
+        <v>50203080</v>
+      </c>
+      <c r="C164" s="182"/>
+      <c r="D164" s="182"/>
+    </row>
+    <row r="165" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="184" t="s">
+        <v>925</v>
+      </c>
+      <c r="B165" s="185">
+        <v>50203090</v>
+      </c>
+      <c r="C165" s="182"/>
+      <c r="D165" s="182"/>
+    </row>
+    <row r="166" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="184" t="s">
+        <v>926</v>
+      </c>
+      <c r="B166" s="185">
+        <v>50203100</v>
+      </c>
+      <c r="C166" s="182"/>
+      <c r="D166" s="182"/>
+    </row>
+    <row r="167" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="184" t="s">
+        <v>927</v>
+      </c>
+      <c r="B167" s="185">
+        <v>50203990</v>
+      </c>
+      <c r="C167" s="182"/>
+      <c r="D167" s="182"/>
+    </row>
+    <row r="168" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B168" s="185">
+        <v>50204010</v>
+      </c>
+      <c r="C168" s="182"/>
+      <c r="D168" s="182"/>
+    </row>
+    <row r="169" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="191" t="s">
+        <v>190</v>
+      </c>
+      <c r="B169" s="192">
+        <v>50204020</v>
+      </c>
+      <c r="C169" s="182"/>
+      <c r="D169" s="182"/>
+    </row>
+    <row r="170" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="191" t="s">
+        <v>928</v>
+      </c>
+      <c r="B170" s="192">
+        <v>50205010</v>
+      </c>
+      <c r="C170" s="182"/>
+      <c r="D170" s="182"/>
+    </row>
+    <row r="171" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="191" t="s">
+        <v>193</v>
+      </c>
+      <c r="B171" s="192">
+        <v>50205020</v>
+      </c>
+      <c r="C171" s="182"/>
+      <c r="D171" s="182"/>
+    </row>
+    <row r="172" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B172" s="192">
+        <v>50205030</v>
+      </c>
+      <c r="C172" s="182"/>
+      <c r="D172" s="182"/>
+    </row>
+    <row r="173" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="191" t="s">
+        <v>929</v>
+      </c>
+      <c r="B173" s="192">
+        <v>50206010</v>
+      </c>
+      <c r="C173" s="182"/>
+      <c r="D173" s="182"/>
+    </row>
+    <row r="174" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="191" t="s">
+        <v>198</v>
+      </c>
+      <c r="B174" s="192">
+        <v>50206020</v>
+      </c>
+      <c r="C174" s="182"/>
+      <c r="D174" s="182"/>
+    </row>
+    <row r="175" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="191" t="s">
+        <v>200</v>
+      </c>
+      <c r="B175" s="192">
+        <v>50207010</v>
+      </c>
+      <c r="C175" s="182"/>
+      <c r="D175" s="182"/>
+    </row>
+    <row r="176" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="191" t="s">
+        <v>930</v>
+      </c>
+      <c r="B176" s="192">
+        <v>50207020</v>
+      </c>
+      <c r="C176" s="182"/>
+      <c r="D176" s="182"/>
+    </row>
+    <row r="177" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="191" t="s">
+        <v>931</v>
+      </c>
+      <c r="B177" s="192">
+        <v>50210030</v>
+      </c>
+      <c r="C177" s="182"/>
+      <c r="D177" s="182"/>
+    </row>
+    <row r="178" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="191" t="s">
+        <v>211</v>
+      </c>
+      <c r="B178" s="192">
+        <v>50211010</v>
+      </c>
+      <c r="C178" s="182"/>
+      <c r="D178" s="182"/>
+    </row>
+    <row r="179" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="191" t="s">
+        <v>212</v>
+      </c>
+      <c r="B179" s="192">
+        <v>50211020</v>
+      </c>
+      <c r="C179" s="182"/>
+      <c r="D179" s="182"/>
+    </row>
+    <row r="180" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="191" t="s">
+        <v>213</v>
+      </c>
+      <c r="B180" s="192">
+        <v>50211030</v>
+      </c>
+      <c r="C180" s="182"/>
+      <c r="D180" s="182"/>
+    </row>
+    <row r="181" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="191" t="s">
+        <v>214</v>
+      </c>
+      <c r="B181" s="192">
+        <v>50211990</v>
+      </c>
+      <c r="C181" s="182"/>
+      <c r="D181" s="182"/>
+    </row>
+    <row r="182" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="191" t="s">
+        <v>218</v>
+      </c>
+      <c r="B182" s="192">
+        <v>50212030</v>
+      </c>
+      <c r="C182" s="182"/>
+      <c r="D182" s="182"/>
+    </row>
+    <row r="183" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="191" t="s">
+        <v>219</v>
+      </c>
+      <c r="B183" s="192">
+        <v>50212990</v>
+      </c>
+      <c r="C183" s="182"/>
+      <c r="D183" s="182"/>
+    </row>
+    <row r="184" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="191" t="s">
+        <v>932</v>
+      </c>
+      <c r="B184" s="192">
+        <v>50213020</v>
+      </c>
+      <c r="C184" s="182"/>
+      <c r="D184" s="182"/>
+    </row>
+    <row r="185" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="191" t="s">
+        <v>933</v>
+      </c>
+      <c r="B185" s="192">
+        <v>50213030</v>
+      </c>
+      <c r="C185" s="182"/>
+      <c r="D185" s="182"/>
+    </row>
+    <row r="186" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="191" t="s">
+        <v>934</v>
+      </c>
+      <c r="B186" s="192">
+        <v>50213040</v>
+      </c>
+      <c r="C186" s="182"/>
+      <c r="D186" s="182"/>
+    </row>
+    <row r="187" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="191" t="s">
+        <v>935</v>
+      </c>
+      <c r="B187" s="192">
+        <v>50213050</v>
+      </c>
+      <c r="C187" s="182"/>
+      <c r="D187" s="182"/>
+    </row>
+    <row r="188" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="191" t="s">
+        <v>936</v>
+      </c>
+      <c r="B188" s="192">
+        <v>50213060</v>
+      </c>
+      <c r="C188" s="182"/>
+      <c r="D188" s="182"/>
+    </row>
+    <row r="189" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="191" t="s">
+        <v>937</v>
+      </c>
+      <c r="B189" s="192">
+        <v>50213070</v>
+      </c>
+      <c r="C189" s="182"/>
+      <c r="D189" s="182"/>
+    </row>
+    <row r="190" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="191" t="s">
+        <v>938</v>
+      </c>
+      <c r="B190" s="192">
+        <v>50213990</v>
+      </c>
+      <c r="C190" s="182"/>
+      <c r="D190" s="182"/>
+    </row>
+    <row r="191" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="191" t="s">
+        <v>939</v>
+      </c>
+      <c r="B191" s="192">
+        <v>50214030</v>
+      </c>
+      <c r="C191" s="182"/>
+      <c r="D191" s="182"/>
+    </row>
+    <row r="192" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="191" t="s">
+        <v>940</v>
+      </c>
+      <c r="B192" s="192">
+        <v>50214060</v>
+      </c>
+      <c r="C192" s="182"/>
+      <c r="D192" s="182"/>
+    </row>
+    <row r="193" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="191" t="s">
+        <v>941</v>
+      </c>
+      <c r="B193" s="192">
+        <v>50215020</v>
+      </c>
+      <c r="C193" s="182"/>
+      <c r="D193" s="182"/>
+    </row>
+    <row r="194" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="191" t="s">
+        <v>942</v>
+      </c>
+      <c r="B194" s="192">
+        <v>50216010</v>
+      </c>
+      <c r="C194" s="182"/>
+      <c r="D194" s="182"/>
+    </row>
+    <row r="195" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="191" t="s">
+        <v>943</v>
+      </c>
+      <c r="B195" s="192">
+        <v>50216020</v>
+      </c>
+      <c r="C195" s="182"/>
+      <c r="D195" s="182"/>
+    </row>
+    <row r="196" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="191" t="s">
+        <v>234</v>
+      </c>
+      <c r="B196" s="192">
+        <v>50216030</v>
+      </c>
+      <c r="C196" s="182"/>
+      <c r="D196" s="182"/>
+    </row>
+    <row r="197" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="191" t="s">
+        <v>236</v>
+      </c>
+      <c r="B197" s="192">
+        <v>50299010</v>
+      </c>
+      <c r="C197" s="182"/>
+      <c r="D197" s="182"/>
+    </row>
+    <row r="198" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="191" t="s">
+        <v>944</v>
+      </c>
+      <c r="B198" s="192">
+        <v>50299020</v>
+      </c>
+      <c r="C198" s="182"/>
+      <c r="D198" s="182"/>
+    </row>
+    <row r="199" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="191" t="s">
+        <v>238</v>
+      </c>
+      <c r="B199" s="192">
+        <v>50299030</v>
+      </c>
+      <c r="C199" s="182"/>
+      <c r="D199" s="182"/>
+    </row>
+    <row r="200" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="191" t="s">
+        <v>240</v>
+      </c>
+      <c r="B200" s="192">
+        <v>50299050</v>
+      </c>
+      <c r="C200" s="182"/>
+      <c r="D200" s="182"/>
+    </row>
+    <row r="201" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="191" t="s">
+        <v>945</v>
+      </c>
+      <c r="B201" s="192">
+        <v>50299060</v>
+      </c>
+      <c r="C201" s="182"/>
+      <c r="D201" s="182"/>
+    </row>
+    <row r="202" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="191" t="s">
+        <v>243</v>
+      </c>
+      <c r="B202" s="192">
+        <v>50299080</v>
+      </c>
+      <c r="C202" s="182"/>
+      <c r="D202" s="182"/>
+    </row>
+    <row r="203" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="191" t="s">
+        <v>946</v>
+      </c>
+      <c r="B203" s="192">
+        <v>50299990</v>
+      </c>
+      <c r="C203" s="182"/>
+      <c r="D203" s="182"/>
+    </row>
+    <row r="204" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="191" t="s">
+        <v>947</v>
+      </c>
+      <c r="B204" s="192">
+        <v>50301990</v>
+      </c>
+      <c r="C204" s="182"/>
+      <c r="D204" s="182"/>
+    </row>
+    <row r="205" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="191" t="s">
+        <v>258</v>
+      </c>
+      <c r="B205" s="192">
+        <v>50501030</v>
+      </c>
+      <c r="C205" s="182"/>
+      <c r="D205" s="182"/>
+    </row>
+    <row r="206" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="191" t="s">
+        <v>948</v>
+      </c>
+      <c r="B206" s="192">
+        <v>50501050</v>
+      </c>
+      <c r="C206" s="182"/>
+      <c r="D206" s="182"/>
+    </row>
+    <row r="207" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="191" t="s">
+        <v>261</v>
+      </c>
+      <c r="B207" s="192">
+        <v>50501060</v>
+      </c>
+      <c r="C207" s="182"/>
+      <c r="D207" s="182"/>
+    </row>
+    <row r="208" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="191" t="s">
+        <v>949</v>
+      </c>
+      <c r="B208" s="192">
+        <v>50501070</v>
+      </c>
+      <c r="C208" s="182"/>
+      <c r="D208" s="182"/>
+    </row>
+    <row r="209" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="191" t="s">
+        <v>950</v>
+      </c>
+      <c r="B209" s="192">
+        <v>50501990</v>
+      </c>
+      <c r="C209" s="182"/>
+      <c r="D209" s="182"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="193"/>
+      <c r="B210" s="194" t="s">
+        <v>951</v>
+      </c>
+      <c r="C210" s="195">
+        <f>SUM(C11:C209)</f>
+        <v>0</v>
+      </c>
+      <c r="D210" s="195">
+        <f>SUM(D11:D204)</f>
+        <v>0</v>
+      </c>
+      <c r="E210" s="189"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="196"/>
+      <c r="B211" s="197"/>
+      <c r="C211" s="198"/>
+      <c r="D211" s="199"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="200" t="s">
+        <v>26</v>
+      </c>
+      <c r="B212" s="273" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" s="273"/>
+      <c r="D212" s="273"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="200"/>
+      <c r="B213" s="179"/>
+      <c r="C213" s="201"/>
+      <c r="D213" s="200"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="200"/>
+      <c r="B214" s="179"/>
+      <c r="C214" s="202"/>
+      <c r="D214" s="200"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="203"/>
+      <c r="B215" s="267" t="s">
+        <v>28</v>
+      </c>
+      <c r="C215" s="267"/>
+      <c r="D215" s="267"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="204"/>
+      <c r="B216" s="268" t="s">
+        <v>29</v>
+      </c>
+      <c r="C216" s="268"/>
+      <c r="D216" s="268"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B215:D215"/>
+    <mergeCell ref="B216:D216"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B212:D212"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>